--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17533084-75FC-EB43-9DB4-249428C1C386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D1F727-1718-BF43-8B32-9F3868ABB800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15640" yWindow="3220" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="48">
   <si>
     <t>總計</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>08/23-08/29</t>
+  </si>
+  <si>
+    <t>26Q4W10</t>
+  </si>
+  <si>
+    <t>08/30-09/05</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1076,9 @@
       <c r="BM1" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="BU1" s="26"/>
+      <c r="BU1" s="26" t="s">
+        <v>46</v>
+      </c>
       <c r="BV1" s="26"/>
       <c r="BX1" s="25"/>
       <c r="CC1" s="26"/>
@@ -1139,6 +1147,9 @@
       <c r="BQ2" s="21"/>
       <c r="BR2" s="21"/>
       <c r="BS2" s="21"/>
+      <c r="BU2" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="BV2" s="21"/>
       <c r="BX2" s="21"/>
       <c r="BY2" s="21"/>
@@ -1358,16 +1369,16 @@
         <v>13</v>
       </c>
       <c r="BU4" s="19" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="BV4" s="19" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="BW4" s="18" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="BX4" s="17" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="BY4" s="16" t="s">
         <v>13</v>
@@ -1645,13 +1656,15 @@
         <v>75</v>
       </c>
       <c r="BV5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="BW5" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="BW5" s="15">
+        <v>5042</v>
+      </c>
       <c r="BX5" s="33"/>
       <c r="BY5" s="10">
         <f t="shared" ref="BY5:BY33" si="20">BW5-BO5</f>
-        <v>-6262</v>
+        <v>-1220</v>
       </c>
       <c r="BZ5" s="12">
         <f t="shared" ref="BZ5:BZ60" si="21">BX5-BP5</f>
@@ -1672,7 +1685,7 @@
       <c r="CF5" s="33"/>
       <c r="CG5" s="10">
         <f t="shared" ref="CG5:CG60" si="23">CE5-BW5</f>
-        <v>0</v>
+        <v>-5042</v>
       </c>
       <c r="CH5" s="12">
         <f t="shared" ref="CH5:CH60" si="24">CF5-BX5</f>
@@ -1899,7 +1912,7 @@
       </c>
       <c r="BU6" s="14"/>
       <c r="BV6" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BX6" s="33"/>
       <c r="BY6" s="10">
@@ -2159,18 +2172,23 @@
       <c r="BV7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX7" s="12"/>
+      <c r="BW7" s="10">
+        <v>198</v>
+      </c>
+      <c r="BX7" s="12">
+        <v>205488</v>
+      </c>
       <c r="BY7" s="10">
         <f t="shared" si="20"/>
-        <v>-209</v>
+        <v>-11</v>
       </c>
       <c r="BZ7" s="12">
         <f t="shared" si="21"/>
-        <v>-210267.61904672001</v>
+        <v>-4779.6190467200067</v>
       </c>
       <c r="CA7" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-2.2731122692068E-2</v>
       </c>
       <c r="CC7" s="14"/>
       <c r="CD7" s="13" t="s">
@@ -2179,15 +2197,15 @@
       <c r="CF7" s="12"/>
       <c r="CG7" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-198</v>
       </c>
       <c r="CH7" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI7" s="11" t="e">
+        <v>-205488</v>
+      </c>
+      <c r="CI7" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK7" s="14"/>
       <c r="CL7" s="13" t="s">
@@ -2417,18 +2435,23 @@
       <c r="BV8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX8" s="12"/>
+      <c r="BW8" s="10">
+        <v>204</v>
+      </c>
+      <c r="BX8" s="12">
+        <v>339810</v>
+      </c>
       <c r="BY8" s="10">
         <f t="shared" si="20"/>
-        <v>-271</v>
+        <v>-67</v>
       </c>
       <c r="BZ8" s="12">
         <f t="shared" si="21"/>
-        <v>-337086.66666618001</v>
+        <v>2723.3333338199882</v>
       </c>
       <c r="CA8" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>8.0790301222947204E-3</v>
       </c>
       <c r="CC8" s="14"/>
       <c r="CD8" s="13" t="s">
@@ -2437,15 +2460,15 @@
       <c r="CF8" s="12"/>
       <c r="CG8" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-204</v>
       </c>
       <c r="CH8" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI8" s="11" t="e">
+        <v>-339810</v>
+      </c>
+      <c r="CI8" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK8" s="14"/>
       <c r="CL8" s="13" t="s">
@@ -2675,18 +2698,23 @@
       <c r="BV9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX9" s="12"/>
+      <c r="BW9" s="10">
+        <v>57</v>
+      </c>
+      <c r="BX9" s="12">
+        <v>396124</v>
+      </c>
       <c r="BY9" s="10">
         <f t="shared" si="20"/>
-        <v>-53</v>
+        <v>4</v>
       </c>
       <c r="BZ9" s="12">
         <f t="shared" si="21"/>
-        <v>-376638.09523803002</v>
+        <v>19485.904761969985</v>
       </c>
       <c r="CA9" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>5.1736414898910225E-2</v>
       </c>
       <c r="CC9" s="14"/>
       <c r="CD9" s="13" t="s">
@@ -2695,15 +2723,15 @@
       <c r="CF9" s="12"/>
       <c r="CG9" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-57</v>
       </c>
       <c r="CH9" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI9" s="11" t="e">
+        <v>-396124</v>
+      </c>
+      <c r="CI9" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK9" s="14"/>
       <c r="CL9" s="13" t="s">
@@ -2933,18 +2961,23 @@
       <c r="BV10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BX10" s="12"/>
+      <c r="BW10" s="10">
+        <v>59</v>
+      </c>
+      <c r="BX10" s="12">
+        <v>495333</v>
+      </c>
       <c r="BY10" s="10">
         <f t="shared" si="20"/>
-        <v>-5</v>
+        <v>54</v>
       </c>
       <c r="BZ10" s="12">
         <f t="shared" si="21"/>
-        <v>-40476.190476169999</v>
+        <v>454856.80952383002</v>
       </c>
       <c r="CA10" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>11.237638823535603</v>
       </c>
       <c r="CC10" s="14"/>
       <c r="CD10" s="13" t="s">
@@ -2953,15 +2986,15 @@
       <c r="CF10" s="12"/>
       <c r="CG10" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-59</v>
       </c>
       <c r="CH10" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI10" s="11" t="e">
+        <v>-495333</v>
+      </c>
+      <c r="CI10" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK10" s="14"/>
       <c r="CL10" s="13" t="s">
@@ -3191,18 +3224,23 @@
       <c r="BV11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX11" s="12"/>
+      <c r="BW11" s="10">
+        <v>6</v>
+      </c>
+      <c r="BX11" s="12">
+        <v>32240</v>
+      </c>
       <c r="BY11" s="10">
         <f t="shared" si="20"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="BZ11" s="12">
         <f t="shared" si="21"/>
-        <v>-21150</v>
+        <v>11090</v>
       </c>
       <c r="CA11" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.52434988179669029</v>
       </c>
       <c r="CC11" s="14"/>
       <c r="CD11" s="13" t="s">
@@ -3211,15 +3249,15 @@
       <c r="CF11" s="12"/>
       <c r="CG11" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="CH11" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI11" s="11" t="e">
+        <v>-32240</v>
+      </c>
+      <c r="CI11" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK11" s="14"/>
       <c r="CL11" s="13" t="s">
@@ -3449,18 +3487,23 @@
       <c r="BV12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX12" s="12"/>
+      <c r="BW12" s="10">
+        <v>29</v>
+      </c>
+      <c r="BX12" s="12">
+        <v>1151102</v>
+      </c>
       <c r="BY12" s="10">
         <f t="shared" si="20"/>
-        <v>-24</v>
+        <v>5</v>
       </c>
       <c r="BZ12" s="12">
         <f t="shared" si="21"/>
-        <v>-798423.80952372996</v>
+        <v>352678.19047627004</v>
       </c>
       <c r="CA12" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.44171802778106917</v>
       </c>
       <c r="CC12" s="14"/>
       <c r="CD12" s="13" t="s">
@@ -3469,15 +3512,15 @@
       <c r="CF12" s="12"/>
       <c r="CG12" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="CH12" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI12" s="11" t="e">
+        <v>-1151102</v>
+      </c>
+      <c r="CI12" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK12" s="14"/>
       <c r="CL12" s="13" t="s">
@@ -3707,18 +3750,23 @@
       <c r="BV13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX13" s="12"/>
+      <c r="BW13" s="10">
+        <v>49</v>
+      </c>
+      <c r="BX13" s="12">
+        <v>1278952</v>
+      </c>
       <c r="BY13" s="10">
         <f t="shared" si="20"/>
-        <v>-45</v>
+        <v>4</v>
       </c>
       <c r="BZ13" s="12">
         <f t="shared" si="21"/>
-        <v>-981238.09523791994</v>
+        <v>297713.90476208006</v>
       </c>
       <c r="CA13" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.30340638648960488</v>
       </c>
       <c r="CC13" s="14"/>
       <c r="CD13" s="13" t="s">
@@ -3727,15 +3775,15 @@
       <c r="CF13" s="12"/>
       <c r="CG13" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="CH13" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI13" s="11" t="e">
+        <v>-1278952</v>
+      </c>
+      <c r="CI13" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK13" s="14"/>
       <c r="CL13" s="13" t="s">
@@ -3965,18 +4013,23 @@
       <c r="BV14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX14" s="12"/>
+      <c r="BW14" s="10">
+        <v>40</v>
+      </c>
+      <c r="BX14" s="12">
+        <v>1330476</v>
+      </c>
       <c r="BY14" s="10">
         <f t="shared" si="20"/>
-        <v>-32</v>
+        <v>8</v>
       </c>
       <c r="BZ14" s="12">
         <f t="shared" si="21"/>
-        <v>-1143619.0476189801</v>
+        <v>186856.95238101995</v>
       </c>
       <c r="CA14" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.16339090606269366</v>
       </c>
       <c r="CC14" s="14"/>
       <c r="CD14" s="13" t="s">
@@ -3985,15 +4038,15 @@
       <c r="CF14" s="12"/>
       <c r="CG14" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="CH14" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI14" s="11" t="e">
+        <v>-1330476</v>
+      </c>
+      <c r="CI14" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK14" s="14"/>
       <c r="CL14" s="13" t="s">
@@ -4221,22 +4274,26 @@
         <v>-8.9533351804416225E-2</v>
       </c>
       <c r="BU15" s="9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="BV15" s="9"/>
-      <c r="BW15" s="8"/>
-      <c r="BX15" s="7"/>
+      <c r="BW15" s="8">
+        <v>642</v>
+      </c>
+      <c r="BX15" s="7">
+        <v>5229525</v>
+      </c>
       <c r="BY15" s="27">
         <f t="shared" si="20"/>
-        <v>-644</v>
+        <v>-2</v>
       </c>
       <c r="BZ15" s="28">
         <f t="shared" si="21"/>
-        <v>-3908899.5238077301</v>
+        <v>1320625.4761922699</v>
       </c>
       <c r="CA15" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.33785096499636413</v>
       </c>
       <c r="CC15" s="9" t="s">
         <v>18</v>
@@ -4246,15 +4303,15 @@
       <c r="CF15" s="7"/>
       <c r="CG15" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-642</v>
       </c>
       <c r="CH15" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI15" s="29" t="e">
+        <v>-5229525</v>
+      </c>
+      <c r="CI15" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK15" s="9" t="s">
         <v>18</v>
@@ -4487,13 +4544,15 @@
         <v>76</v>
       </c>
       <c r="BV16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="BW16" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="BW16" s="15">
+        <v>3854</v>
+      </c>
       <c r="BX16" s="33"/>
       <c r="BY16" s="10">
         <f t="shared" si="20"/>
-        <v>-3936</v>
+        <v>-82</v>
       </c>
       <c r="BZ16" s="12">
         <f t="shared" si="21"/>
@@ -4513,7 +4572,7 @@
       <c r="CF16" s="33"/>
       <c r="CG16" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-3854</v>
       </c>
       <c r="CH16" s="12">
         <f t="shared" si="24"/>
@@ -4738,7 +4797,7 @@
       </c>
       <c r="BU17" s="14"/>
       <c r="BV17" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BW17" s="15"/>
       <c r="BX17" s="33"/>
@@ -5002,18 +5061,23 @@
       <c r="BV18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX18" s="12"/>
+      <c r="BW18" s="10">
+        <v>139</v>
+      </c>
+      <c r="BX18" s="12">
+        <v>140534</v>
+      </c>
       <c r="BY18" s="10">
         <f t="shared" si="20"/>
-        <v>-129</v>
+        <v>10</v>
       </c>
       <c r="BZ18" s="12">
         <f t="shared" si="21"/>
-        <v>-116457.14285663</v>
+        <v>24076.857143369998</v>
       </c>
       <c r="CA18" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.20674435721826814</v>
       </c>
       <c r="CC18" s="14"/>
       <c r="CD18" s="13" t="s">
@@ -5022,15 +5086,15 @@
       <c r="CF18" s="12"/>
       <c r="CG18" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-139</v>
       </c>
       <c r="CH18" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI18" s="11" t="e">
+        <v>-140534</v>
+      </c>
+      <c r="CI18" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK18" s="14"/>
       <c r="CL18" s="13" t="s">
@@ -5260,18 +5324,23 @@
       <c r="BV19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX19" s="12"/>
+      <c r="BW19" s="10">
+        <v>183</v>
+      </c>
+      <c r="BX19" s="12">
+        <v>189429</v>
+      </c>
       <c r="BY19" s="10">
         <f t="shared" si="20"/>
-        <v>-164</v>
+        <v>19</v>
       </c>
       <c r="BZ19" s="12">
         <f t="shared" si="21"/>
-        <v>-177323.80952340999</v>
+        <v>12105.190476590011</v>
       </c>
       <c r="CA19" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>6.8266018585574684E-2</v>
       </c>
       <c r="CC19" s="14"/>
       <c r="CD19" s="13" t="s">
@@ -5280,15 +5349,15 @@
       <c r="CF19" s="12"/>
       <c r="CG19" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-183</v>
       </c>
       <c r="CH19" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI19" s="11" t="e">
+        <v>-189429</v>
+      </c>
+      <c r="CI19" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK19" s="14"/>
       <c r="CL19" s="13" t="s">
@@ -5518,18 +5587,23 @@
       <c r="BV20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX20" s="12"/>
+      <c r="BW20" s="10">
+        <v>23</v>
+      </c>
+      <c r="BX20" s="12">
+        <v>131210</v>
+      </c>
       <c r="BY20" s="10">
         <f t="shared" si="20"/>
-        <v>-36</v>
+        <v>-13</v>
       </c>
       <c r="BZ20" s="12">
         <f t="shared" si="21"/>
-        <v>-221085.71428565</v>
+        <v>-89875.71428565</v>
       </c>
       <c r="CA20" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.40651977255087424</v>
       </c>
       <c r="CC20" s="14"/>
       <c r="CD20" s="13" t="s">
@@ -5538,15 +5612,15 @@
       <c r="CF20" s="12"/>
       <c r="CG20" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="CH20" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI20" s="11" t="e">
+        <v>-131210</v>
+      </c>
+      <c r="CI20" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK20" s="14"/>
       <c r="CL20" s="13" t="s">
@@ -5776,18 +5850,23 @@
       <c r="BV21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BX21" s="12"/>
+      <c r="BW21" s="10">
+        <v>1</v>
+      </c>
+      <c r="BX21" s="12">
+        <v>7524</v>
+      </c>
       <c r="BY21" s="10">
         <f t="shared" si="20"/>
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="BZ21" s="12">
         <f t="shared" si="21"/>
-        <v>-67809.523809480001</v>
+        <v>-60285.523809480001</v>
       </c>
       <c r="CA21" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.88904213483138894</v>
       </c>
       <c r="CC21" s="14"/>
       <c r="CD21" s="13" t="s">
@@ -5796,15 +5875,15 @@
       <c r="CF21" s="12"/>
       <c r="CG21" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CH21" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI21" s="11" t="e">
+        <v>-7524</v>
+      </c>
+      <c r="CI21" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK21" s="14"/>
       <c r="CL21" s="13" t="s">
@@ -6034,18 +6113,23 @@
       <c r="BV22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX22" s="12"/>
+      <c r="BW22" s="10">
+        <v>12</v>
+      </c>
+      <c r="BX22" s="12">
+        <v>67380</v>
+      </c>
       <c r="BY22" s="10">
         <f t="shared" si="20"/>
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="BZ22" s="12">
         <f t="shared" si="21"/>
-        <v>-78308</v>
+        <v>-10928</v>
       </c>
       <c r="CA22" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.13955151453235939</v>
       </c>
       <c r="CC22" s="14"/>
       <c r="CD22" s="13" t="s">
@@ -6054,15 +6138,15 @@
       <c r="CF22" s="12"/>
       <c r="CG22" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="CH22" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI22" s="11" t="e">
+        <v>-67380</v>
+      </c>
+      <c r="CI22" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK22" s="14"/>
       <c r="CL22" s="13" t="s">
@@ -6292,18 +6376,23 @@
       <c r="BV23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX23" s="12"/>
+      <c r="BW23" s="10">
+        <v>24</v>
+      </c>
+      <c r="BX23" s="12">
+        <v>731464</v>
+      </c>
       <c r="BY23" s="10">
         <f t="shared" si="20"/>
-        <v>-16</v>
+        <v>8</v>
       </c>
       <c r="BZ23" s="12">
         <f t="shared" si="21"/>
-        <v>-555333.33333324001</v>
+        <v>176130.66666675999</v>
       </c>
       <c r="CA23" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.31716206482615172</v>
       </c>
       <c r="CC23" s="14"/>
       <c r="CD23" s="13" t="s">
@@ -6312,15 +6401,15 @@
       <c r="CF23" s="12"/>
       <c r="CG23" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="CH23" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI23" s="11" t="e">
+        <v>-731464</v>
+      </c>
+      <c r="CI23" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK23" s="14"/>
       <c r="CL23" s="13" t="s">
@@ -6550,18 +6639,23 @@
       <c r="BV24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX24" s="12"/>
+      <c r="BW24" s="10">
+        <v>28</v>
+      </c>
+      <c r="BX24" s="12">
+        <v>737238</v>
+      </c>
       <c r="BY24" s="10">
         <f t="shared" si="20"/>
-        <v>-28</v>
+        <v>0</v>
       </c>
       <c r="BZ24" s="12">
         <f t="shared" si="21"/>
-        <v>-591904.76190464001</v>
+        <v>145333.23809535999</v>
       </c>
       <c r="CA24" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.2455348350766845</v>
       </c>
       <c r="CC24" s="14"/>
       <c r="CD24" s="13" t="s">
@@ -6570,15 +6664,15 @@
       <c r="CF24" s="12"/>
       <c r="CG24" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="CH24" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI24" s="11" t="e">
+        <v>-737238</v>
+      </c>
+      <c r="CI24" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK24" s="14"/>
       <c r="CL24" s="13" t="s">
@@ -6808,18 +6902,23 @@
       <c r="BV25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX25" s="12"/>
+      <c r="BW25" s="10">
+        <v>27</v>
+      </c>
+      <c r="BX25" s="12">
+        <v>927717</v>
+      </c>
       <c r="BY25" s="10">
         <f t="shared" si="20"/>
-        <v>-34</v>
+        <v>-7</v>
       </c>
       <c r="BZ25" s="12">
         <f t="shared" si="21"/>
-        <v>-1225333.3333332599</v>
+        <v>-297616.33333325991</v>
       </c>
       <c r="CA25" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.24288601741018315</v>
       </c>
       <c r="CC25" s="14"/>
       <c r="CD25" s="13" t="s">
@@ -6828,15 +6927,15 @@
       <c r="CF25" s="12"/>
       <c r="CG25" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="CH25" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI25" s="11" t="e">
+        <v>-927717</v>
+      </c>
+      <c r="CI25" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK25" s="14"/>
       <c r="CL25" s="13" t="s">
@@ -7067,19 +7166,23 @@
         <v>12</v>
       </c>
       <c r="BV26" s="9"/>
-      <c r="BW26" s="8"/>
-      <c r="BX26" s="7"/>
+      <c r="BW26" s="8">
+        <v>437</v>
+      </c>
+      <c r="BX26" s="7">
+        <v>2932496</v>
+      </c>
       <c r="BY26" s="27">
         <f t="shared" si="20"/>
-        <v>-429</v>
+        <v>8</v>
       </c>
       <c r="BZ26" s="28">
         <f t="shared" si="21"/>
-        <v>-3033555.61904631</v>
+        <v>-101059.61904630996</v>
       </c>
       <c r="CA26" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-3.331391665008638E-2</v>
       </c>
       <c r="CC26" s="9" t="s">
         <v>12</v>
@@ -7089,15 +7192,15 @@
       <c r="CF26" s="7"/>
       <c r="CG26" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-437</v>
       </c>
       <c r="CH26" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI26" s="29" t="e">
+        <v>-2932496</v>
+      </c>
+      <c r="CI26" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK26" s="9" t="s">
         <v>12</v>
@@ -7330,13 +7433,15 @@
         <v>77</v>
       </c>
       <c r="BV27" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="BW27" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="BW27" s="15">
+        <v>2744</v>
+      </c>
       <c r="BX27" s="33"/>
       <c r="BY27" s="10">
         <f t="shared" si="20"/>
-        <v>-3175</v>
+        <v>-431</v>
       </c>
       <c r="BZ27" s="12">
         <f t="shared" si="21"/>
@@ -7356,7 +7461,7 @@
       <c r="CF27" s="33"/>
       <c r="CG27" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-2744</v>
       </c>
       <c r="CH27" s="12">
         <f t="shared" si="24"/>
@@ -7581,7 +7686,7 @@
       </c>
       <c r="BU28" s="14"/>
       <c r="BV28" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BW28" s="15"/>
       <c r="BX28" s="33"/>
@@ -7845,18 +7950,23 @@
       <c r="BV29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX29" s="12"/>
+      <c r="BW29" s="10">
+        <v>86</v>
+      </c>
+      <c r="BX29" s="12">
+        <v>95122</v>
+      </c>
       <c r="BY29" s="10">
         <f t="shared" si="20"/>
-        <v>-66</v>
+        <v>20</v>
       </c>
       <c r="BZ29" s="12">
         <f t="shared" si="21"/>
-        <v>-56596.190475900003</v>
+        <v>38525.809524099997</v>
       </c>
       <c r="CA29" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.68071382897237931</v>
       </c>
       <c r="CC29" s="14"/>
       <c r="CD29" s="13" t="s">
@@ -7865,15 +7975,15 @@
       <c r="CF29" s="12"/>
       <c r="CG29" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-86</v>
       </c>
       <c r="CH29" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI29" s="11" t="e">
+        <v>-95122</v>
+      </c>
+      <c r="CI29" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK29" s="14"/>
       <c r="CL29" s="13" t="s">
@@ -8103,18 +8213,23 @@
       <c r="BV30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX30" s="12"/>
+      <c r="BW30" s="10">
+        <v>61</v>
+      </c>
+      <c r="BX30" s="12">
+        <v>52987</v>
+      </c>
       <c r="BY30" s="10">
         <f t="shared" si="20"/>
-        <v>-66</v>
+        <v>-5</v>
       </c>
       <c r="BZ30" s="12">
         <f t="shared" si="21"/>
-        <v>-72428.571428359995</v>
+        <v>-19441.571428359995</v>
       </c>
       <c r="CA30" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.26842406311423522</v>
       </c>
       <c r="CC30" s="14"/>
       <c r="CD30" s="13" t="s">
@@ -8123,15 +8238,15 @@
       <c r="CF30" s="12"/>
       <c r="CG30" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-61</v>
       </c>
       <c r="CH30" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI30" s="11" t="e">
+        <v>-52987</v>
+      </c>
+      <c r="CI30" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK30" s="14"/>
       <c r="CL30" s="13" t="s">
@@ -8361,18 +8476,23 @@
       <c r="BV31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX31" s="12"/>
+      <c r="BW31" s="10">
+        <v>16</v>
+      </c>
+      <c r="BX31" s="12">
+        <v>102048</v>
+      </c>
       <c r="BY31" s="10">
         <f t="shared" si="20"/>
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="BZ31" s="12">
         <f t="shared" si="21"/>
-        <v>-130314.28571421999</v>
+        <v>-28266.285714219994</v>
       </c>
       <c r="CA31" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.21690857268103458</v>
       </c>
       <c r="CC31" s="14"/>
       <c r="CD31" s="13" t="s">
@@ -8381,15 +8501,15 @@
       <c r="CF31" s="12"/>
       <c r="CG31" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="CH31" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI31" s="11" t="e">
+        <v>-102048</v>
+      </c>
+      <c r="CI31" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK31" s="14"/>
       <c r="CL31" s="13" t="s">
@@ -8619,18 +8739,23 @@
       <c r="BV32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BX32" s="12"/>
+      <c r="BW32" s="10">
+        <v>3</v>
+      </c>
+      <c r="BX32" s="12">
+        <v>27333</v>
+      </c>
       <c r="BY32" s="10">
         <f t="shared" si="20"/>
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="BZ32" s="12">
         <f t="shared" si="21"/>
-        <v>-83999.999999959997</v>
+        <v>-56666.999999959997</v>
       </c>
       <c r="CA32" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.67460714285698786</v>
       </c>
       <c r="CC32" s="14"/>
       <c r="CD32" s="13" t="s">
@@ -8639,15 +8764,15 @@
       <c r="CF32" s="12"/>
       <c r="CG32" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="CH32" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI32" s="11" t="e">
+        <v>-27333</v>
+      </c>
+      <c r="CI32" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK32" s="14"/>
       <c r="CL32" s="13" t="s">
@@ -8877,7 +9002,12 @@
       <c r="BV33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX33" s="12"/>
+      <c r="BW33" s="10">
+        <v>0</v>
+      </c>
+      <c r="BX33" s="12">
+        <v>0</v>
+      </c>
       <c r="BY33" s="10">
         <f t="shared" si="20"/>
         <v>-1</v>
@@ -9135,18 +9265,23 @@
       <c r="BV34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX34" s="12"/>
+      <c r="BW34" s="10">
+        <v>6</v>
+      </c>
+      <c r="BX34" s="12">
+        <v>173517</v>
+      </c>
       <c r="BY34" s="10">
         <f t="shared" ref="BY34:BY60" si="32">BW34-BO34</f>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="BZ34" s="12">
         <f t="shared" si="21"/>
-        <v>-70190.476190460002</v>
+        <v>103326.52380954</v>
       </c>
       <c r="CA34" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>1.4720875169612215</v>
       </c>
       <c r="CC34" s="14"/>
       <c r="CD34" s="13" t="s">
@@ -9155,15 +9290,15 @@
       <c r="CF34" s="12"/>
       <c r="CG34" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="CH34" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI34" s="11" t="e">
+        <v>-173517</v>
+      </c>
+      <c r="CI34" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK34" s="14"/>
       <c r="CL34" s="13" t="s">
@@ -9393,18 +9528,23 @@
       <c r="BV35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX35" s="12"/>
+      <c r="BW35" s="10">
+        <v>6</v>
+      </c>
+      <c r="BX35" s="12">
+        <v>121143</v>
+      </c>
       <c r="BY35" s="10">
         <f t="shared" si="32"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="BZ35" s="12">
         <f t="shared" si="21"/>
-        <v>-160476.19047617001</v>
+        <v>-39333.190476170013</v>
       </c>
       <c r="CA35" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.24510296735895418</v>
       </c>
       <c r="CC35" s="14"/>
       <c r="CD35" s="13" t="s">
@@ -9413,15 +9553,15 @@
       <c r="CF35" s="12"/>
       <c r="CG35" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="CH35" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI35" s="11" t="e">
+        <v>-121143</v>
+      </c>
+      <c r="CI35" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK35" s="14"/>
       <c r="CL35" s="13" t="s">
@@ -9651,18 +9791,23 @@
       <c r="BV36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX36" s="12"/>
+      <c r="BW36" s="10">
+        <v>9</v>
+      </c>
+      <c r="BX36" s="12">
+        <v>324290</v>
+      </c>
       <c r="BY36" s="10">
         <f t="shared" si="32"/>
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="BZ36" s="12">
         <f t="shared" si="21"/>
-        <v>-280190.47619045997</v>
+        <v>44099.523809540027</v>
       </c>
       <c r="CA36" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.15739123045553946</v>
       </c>
       <c r="CC36" s="14"/>
       <c r="CD36" s="13" t="s">
@@ -9671,15 +9816,15 @@
       <c r="CF36" s="12"/>
       <c r="CG36" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="CH36" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI36" s="11" t="e">
+        <v>-324290</v>
+      </c>
+      <c r="CI36" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK36" s="14"/>
       <c r="CL36" s="13" t="s">
@@ -9910,19 +10055,23 @@
         <v>11</v>
       </c>
       <c r="BV37" s="9"/>
-      <c r="BW37" s="8"/>
-      <c r="BX37" s="7"/>
+      <c r="BW37" s="8">
+        <v>187</v>
+      </c>
+      <c r="BX37" s="7">
+        <v>896440</v>
+      </c>
       <c r="BY37" s="27">
         <f t="shared" si="32"/>
-        <v>-174</v>
+        <v>13</v>
       </c>
       <c r="BZ37" s="28">
         <f t="shared" si="21"/>
-        <v>-855186.19047552999</v>
+        <v>41253.809524470009</v>
       </c>
       <c r="CA37" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>4.8239564651448186E-2</v>
       </c>
       <c r="CC37" s="9" t="s">
         <v>11</v>
@@ -9932,15 +10081,15 @@
       <c r="CF37" s="7"/>
       <c r="CG37" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-187</v>
       </c>
       <c r="CH37" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI37" s="29" t="e">
+        <v>-896440</v>
+      </c>
+      <c r="CI37" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK37" s="9" t="s">
         <v>11</v>
@@ -10173,13 +10322,15 @@
         <v>81</v>
       </c>
       <c r="BV38" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="BW38" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="BW38" s="15">
+        <v>1732</v>
+      </c>
       <c r="BX38" s="33"/>
       <c r="BY38" s="10">
         <f t="shared" si="32"/>
-        <v>-1672</v>
+        <v>60</v>
       </c>
       <c r="BZ38" s="12">
         <f t="shared" si="21"/>
@@ -10199,7 +10350,7 @@
       <c r="CF38" s="33"/>
       <c r="CG38" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-1732</v>
       </c>
       <c r="CH38" s="12">
         <f t="shared" si="24"/>
@@ -10424,7 +10575,7 @@
       </c>
       <c r="BU39" s="14"/>
       <c r="BV39" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BW39" s="15"/>
       <c r="BX39" s="33"/>
@@ -10688,18 +10839,23 @@
       <c r="BV40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX40" s="12"/>
+      <c r="BW40" s="10">
+        <v>79</v>
+      </c>
+      <c r="BX40" s="12">
+        <v>66290</v>
+      </c>
       <c r="BY40" s="10">
         <f t="shared" si="32"/>
-        <v>-104</v>
+        <v>-25</v>
       </c>
       <c r="BZ40" s="12">
         <f t="shared" si="21"/>
-        <v>-76006.666666129997</v>
+        <v>-9716.6666661299969</v>
       </c>
       <c r="CA40" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.12783966318128154</v>
       </c>
       <c r="CC40" s="14"/>
       <c r="CD40" s="13" t="s">
@@ -10708,15 +10864,15 @@
       <c r="CF40" s="12"/>
       <c r="CG40" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-79</v>
       </c>
       <c r="CH40" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI40" s="11" t="e">
+        <v>-66290</v>
+      </c>
+      <c r="CI40" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK40" s="14"/>
       <c r="CL40" s="13" t="s">
@@ -10946,18 +11102,23 @@
       <c r="BV41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX41" s="12"/>
+      <c r="BW41" s="10">
+        <v>98</v>
+      </c>
+      <c r="BX41" s="12">
+        <v>87552</v>
+      </c>
       <c r="BY41" s="10">
         <f t="shared" si="32"/>
-        <v>-66</v>
+        <v>32</v>
       </c>
       <c r="BZ41" s="12">
         <f t="shared" si="21"/>
-        <v>-85561.90476166</v>
+        <v>1990.0952383399999</v>
       </c>
       <c r="CA41" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>2.3259127340416047E-2</v>
       </c>
       <c r="CC41" s="14"/>
       <c r="CD41" s="13" t="s">
@@ -10966,15 +11127,15 @@
       <c r="CF41" s="12"/>
       <c r="CG41" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-98</v>
       </c>
       <c r="CH41" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI41" s="11" t="e">
+        <v>-87552</v>
+      </c>
+      <c r="CI41" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK41" s="14"/>
       <c r="CL41" s="13" t="s">
@@ -11204,18 +11365,23 @@
       <c r="BV42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX42" s="12"/>
+      <c r="BW42" s="10">
+        <v>11</v>
+      </c>
+      <c r="BX42" s="12">
+        <v>61324</v>
+      </c>
       <c r="BY42" s="10">
         <f t="shared" si="32"/>
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="BZ42" s="12">
         <f t="shared" si="21"/>
-        <v>-27104.761904750001</v>
+        <v>34219.238095249995</v>
       </c>
       <c r="CA42" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>1.2624806746320547</v>
       </c>
       <c r="CC42" s="14"/>
       <c r="CD42" s="13" t="s">
@@ -11224,15 +11390,15 @@
       <c r="CF42" s="12"/>
       <c r="CG42" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="CH42" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI42" s="11" t="e">
+        <v>-61324</v>
+      </c>
+      <c r="CI42" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK42" s="14"/>
       <c r="CL42" s="13" t="s">
@@ -11462,18 +11628,23 @@
       <c r="BV43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BX43" s="12"/>
+      <c r="BW43" s="10">
+        <v>3</v>
+      </c>
+      <c r="BX43" s="12">
+        <v>27333</v>
+      </c>
       <c r="BY43" s="10">
         <f t="shared" si="32"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="BZ43" s="12">
         <f t="shared" si="21"/>
-        <v>-16952.380952380001</v>
+        <v>10380.619047619999</v>
       </c>
       <c r="CA43" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.61233988764053993</v>
       </c>
       <c r="CC43" s="14"/>
       <c r="CD43" s="13" t="s">
@@ -11482,15 +11653,15 @@
       <c r="CF43" s="12"/>
       <c r="CG43" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="CH43" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI43" s="11" t="e">
+        <v>-27333</v>
+      </c>
+      <c r="CI43" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK43" s="14"/>
       <c r="CL43" s="13" t="s">
@@ -11720,18 +11891,23 @@
       <c r="BV44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX44" s="12"/>
+      <c r="BW44" s="10">
+        <v>2</v>
+      </c>
+      <c r="BX44" s="12">
+        <v>10680</v>
+      </c>
       <c r="BY44" s="10">
         <f t="shared" si="32"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BZ44" s="12">
         <f t="shared" si="21"/>
-        <v>-4608</v>
+        <v>6072</v>
       </c>
       <c r="CA44" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>1.3177083333333333</v>
       </c>
       <c r="CC44" s="14"/>
       <c r="CD44" s="13" t="s">
@@ -11741,15 +11917,15 @@
       <c r="CF44" s="50"/>
       <c r="CG44" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CH44" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI44" s="11" t="e">
+        <v>-10680</v>
+      </c>
+      <c r="CI44" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK44" s="14"/>
       <c r="CL44" s="13" t="s">
@@ -11979,18 +12155,23 @@
       <c r="BV45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX45" s="12"/>
+      <c r="BW45" s="10">
+        <v>8</v>
+      </c>
+      <c r="BX45" s="12">
+        <v>258722</v>
+      </c>
       <c r="BY45" s="10">
         <f t="shared" si="32"/>
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="BZ45" s="12">
         <f t="shared" si="21"/>
-        <v>-214542.85714281001</v>
+        <v>44179.142857189989</v>
       </c>
       <c r="CA45" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.20592222666160465</v>
       </c>
       <c r="CC45" s="14"/>
       <c r="CD45" s="13" t="s">
@@ -12000,15 +12181,15 @@
       <c r="CF45" s="50"/>
       <c r="CG45" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="CH45" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI45" s="11" t="e">
+        <v>-258722</v>
+      </c>
+      <c r="CI45" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK45" s="14"/>
       <c r="CL45" s="13" t="s">
@@ -12238,18 +12419,23 @@
       <c r="BV46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX46" s="12"/>
+      <c r="BW46" s="10">
+        <v>9</v>
+      </c>
+      <c r="BX46" s="12">
+        <v>187810</v>
+      </c>
       <c r="BY46" s="10">
         <f t="shared" si="32"/>
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="BZ46" s="12">
         <f t="shared" si="21"/>
-        <v>-245238.09523802</v>
+        <v>-57428.095238020003</v>
       </c>
       <c r="CA46" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.23417281553374564</v>
       </c>
       <c r="CC46" s="14"/>
       <c r="CD46" s="13" t="s">
@@ -12259,15 +12445,15 @@
       <c r="CF46" s="50"/>
       <c r="CG46" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="CH46" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI46" s="11" t="e">
+        <v>-187810</v>
+      </c>
+      <c r="CI46" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK46" s="14"/>
       <c r="CL46" s="13" t="s">
@@ -12497,18 +12683,23 @@
       <c r="BV47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX47" s="12"/>
+      <c r="BW47" s="10">
+        <v>15</v>
+      </c>
+      <c r="BX47" s="12">
+        <v>498571</v>
+      </c>
       <c r="BY47" s="10">
         <f t="shared" si="32"/>
-        <v>-22</v>
+        <v>-7</v>
       </c>
       <c r="BZ47" s="12">
         <f t="shared" si="21"/>
-        <v>-702493.33333330997</v>
+        <v>-203922.33333330997</v>
       </c>
       <c r="CA47" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.29028365630988207</v>
       </c>
       <c r="CC47" s="14"/>
       <c r="CD47" s="13" t="s">
@@ -12518,15 +12709,15 @@
       <c r="CF47" s="50"/>
       <c r="CG47" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="CH47" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI47" s="11" t="e">
+        <v>-498571</v>
+      </c>
+      <c r="CI47" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK47" s="14"/>
       <c r="CL47" s="13" t="s">
@@ -12757,19 +12948,23 @@
         <v>10</v>
       </c>
       <c r="BV48" s="9"/>
-      <c r="BW48" s="8"/>
-      <c r="BX48" s="7"/>
+      <c r="BW48" s="8">
+        <v>225</v>
+      </c>
+      <c r="BX48" s="7">
+        <v>1198282</v>
+      </c>
       <c r="BY48" s="27">
         <f t="shared" si="32"/>
-        <v>-220</v>
+        <v>5</v>
       </c>
       <c r="BZ48" s="28">
         <f t="shared" si="21"/>
-        <v>-1372507.9999990601</v>
+        <v>-174225.99999906006</v>
       </c>
       <c r="CA48" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.12693987940265514</v>
       </c>
       <c r="CC48" s="9" t="s">
         <v>10</v>
@@ -12779,15 +12974,15 @@
       <c r="CF48" s="51"/>
       <c r="CG48" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-225</v>
       </c>
       <c r="CH48" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI48" s="29" t="e">
+        <v>-1198282</v>
+      </c>
+      <c r="CI48" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK48" s="9" t="s">
         <v>10</v>
@@ -12994,7 +13189,7 @@
         <v>84</v>
       </c>
       <c r="BV49" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="BW49" s="15"/>
       <c r="BX49" s="33"/>
@@ -13245,7 +13440,7 @@
       </c>
       <c r="BU50" s="14"/>
       <c r="BV50" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BW50" s="15"/>
       <c r="BX50" s="33"/>
@@ -13509,18 +13704,23 @@
       <c r="BV51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="BX51" s="12"/>
+      <c r="BW51" s="10">
+        <v>104</v>
+      </c>
+      <c r="BX51" s="12">
+        <v>95841</v>
+      </c>
       <c r="BY51" s="10">
         <f t="shared" si="32"/>
-        <v>-109</v>
+        <v>-5</v>
       </c>
       <c r="BZ51" s="12">
         <f t="shared" si="21"/>
-        <v>-108975.23809471</v>
+        <v>-13134.238094710003</v>
       </c>
       <c r="CA51" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.1205249772732323</v>
       </c>
       <c r="CC51" s="14"/>
       <c r="CD51" s="13" t="s">
@@ -13529,15 +13729,15 @@
       <c r="CF51" s="12"/>
       <c r="CG51" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-104</v>
       </c>
       <c r="CH51" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI51" s="11" t="e">
+        <v>-95841</v>
+      </c>
+      <c r="CI51" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK51" s="14"/>
       <c r="CL51" s="13" t="s">
@@ -13767,18 +13967,23 @@
       <c r="BV52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="BX52" s="12"/>
+      <c r="BW52" s="10">
+        <v>63</v>
+      </c>
+      <c r="BX52" s="12">
+        <v>89305</v>
+      </c>
       <c r="BY52" s="10">
         <f t="shared" si="32"/>
-        <v>-76</v>
+        <v>-13</v>
       </c>
       <c r="BZ52" s="12">
         <f t="shared" si="21"/>
-        <v>-76523.809523589996</v>
+        <v>12781.190476410004</v>
       </c>
       <c r="CA52" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.167022401994636</v>
       </c>
       <c r="CC52" s="14"/>
       <c r="CD52" s="13" t="s">
@@ -13787,15 +13992,15 @@
       <c r="CF52" s="12"/>
       <c r="CG52" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="CH52" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI52" s="11" t="e">
+        <v>-89305</v>
+      </c>
+      <c r="CI52" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK52" s="14"/>
       <c r="CL52" s="13" t="s">
@@ -14025,18 +14230,23 @@
       <c r="BV53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="BX53" s="12"/>
+      <c r="BW53" s="10">
+        <v>6</v>
+      </c>
+      <c r="BX53" s="12">
+        <v>35657</v>
+      </c>
       <c r="BY53" s="10">
         <f t="shared" si="32"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="BZ53" s="12">
         <f t="shared" si="21"/>
-        <v>-51958.095238069996</v>
+        <v>-16301.095238069996</v>
       </c>
       <c r="CA53" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.31373542781695524</v>
       </c>
       <c r="CC53" s="14"/>
       <c r="CD53" s="13" t="s">
@@ -14045,15 +14255,15 @@
       <c r="CF53" s="12"/>
       <c r="CG53" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="CH53" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI53" s="11" t="e">
+        <v>-35657</v>
+      </c>
+      <c r="CI53" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK53" s="14"/>
       <c r="CL53" s="13" t="s">
@@ -14283,18 +14493,23 @@
       <c r="BV54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="BX54" s="12"/>
+      <c r="BW54" s="10">
+        <v>2</v>
+      </c>
+      <c r="BX54" s="12">
+        <v>15048</v>
+      </c>
       <c r="BY54" s="10">
         <f t="shared" si="32"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="BZ54" s="12">
         <f t="shared" si="21"/>
-        <v>-22571.4285714</v>
+        <v>-7523.4285713999998</v>
       </c>
       <c r="CA54" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.33331645569535862</v>
       </c>
       <c r="CC54" s="14"/>
       <c r="CD54" s="13" t="s">
@@ -14303,15 +14518,15 @@
       <c r="CF54" s="12"/>
       <c r="CG54" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CH54" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI54" s="11" t="e">
+        <v>-15048</v>
+      </c>
+      <c r="CI54" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK54" s="14"/>
       <c r="CL54" s="13" t="s">
@@ -14541,18 +14756,23 @@
       <c r="BV55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="BX55" s="12"/>
+      <c r="BW55" s="10">
+        <v>3</v>
+      </c>
+      <c r="BX55" s="12">
+        <v>13770</v>
+      </c>
       <c r="BY55" s="10">
         <f t="shared" si="32"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="BZ55" s="12">
         <f t="shared" si="21"/>
-        <v>-9680</v>
+        <v>4090</v>
       </c>
       <c r="CA55" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.4225206611570248</v>
       </c>
       <c r="CC55" s="14"/>
       <c r="CD55" s="13" t="s">
@@ -14562,15 +14782,15 @@
       <c r="CF55" s="50"/>
       <c r="CG55" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="CH55" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI55" s="11" t="e">
+        <v>-13770</v>
+      </c>
+      <c r="CI55" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK55" s="14"/>
       <c r="CL55" s="13" t="s">
@@ -14800,18 +15020,23 @@
       <c r="BV56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="BX56" s="12"/>
+      <c r="BW56" s="10">
+        <v>5</v>
+      </c>
+      <c r="BX56" s="12">
+        <v>170368</v>
+      </c>
       <c r="BY56" s="10">
         <f t="shared" si="32"/>
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="BZ56" s="12">
         <f t="shared" si="21"/>
-        <v>-273257.1428571</v>
+        <v>-102889.1428571</v>
       </c>
       <c r="CA56" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.37652864910069689</v>
       </c>
       <c r="CC56" s="14"/>
       <c r="CD56" s="13" t="s">
@@ -14821,15 +15046,15 @@
       <c r="CF56" s="50"/>
       <c r="CG56" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CH56" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI56" s="11" t="e">
+        <v>-170368</v>
+      </c>
+      <c r="CI56" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK56" s="14"/>
       <c r="CL56" s="13" t="s">
@@ -15059,18 +15284,23 @@
       <c r="BV57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="BX57" s="12"/>
+      <c r="BW57" s="10">
+        <v>8</v>
+      </c>
+      <c r="BX57" s="12">
+        <v>152095</v>
+      </c>
       <c r="BY57" s="10">
         <f t="shared" si="32"/>
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="BZ57" s="12">
         <f t="shared" si="21"/>
-        <v>-318857.14285708999</v>
+        <v>-166762.14285708999</v>
       </c>
       <c r="CA57" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.52299955197124703</v>
       </c>
       <c r="CC57" s="14"/>
       <c r="CD57" s="13" t="s">
@@ -15080,15 +15310,15 @@
       <c r="CF57" s="50"/>
       <c r="CG57" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="CH57" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI57" s="11" t="e">
+        <v>-152095</v>
+      </c>
+      <c r="CI57" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK57" s="14"/>
       <c r="CL57" s="13" t="s">
@@ -15318,18 +15548,23 @@
       <c r="BV58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="BX58" s="12"/>
+      <c r="BW58" s="10">
+        <v>12</v>
+      </c>
+      <c r="BX58" s="12">
+        <v>365524</v>
+      </c>
       <c r="BY58" s="10">
         <f t="shared" si="32"/>
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="BZ58" s="12">
         <f t="shared" si="21"/>
-        <v>-284857.14285712998</v>
+        <v>80666.857142870023</v>
       </c>
       <c r="CA58" s="11">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>0.28318355065201389</v>
       </c>
       <c r="CC58" s="14"/>
       <c r="CD58" s="13" t="s">
@@ -15339,15 +15574,15 @@
       <c r="CF58" s="50"/>
       <c r="CG58" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="CH58" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI58" s="11" t="e">
+        <v>-365524</v>
+      </c>
+      <c r="CI58" s="11">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK58" s="14"/>
       <c r="CL58" s="13" t="s">
@@ -15578,19 +15813,23 @@
         <v>1</v>
       </c>
       <c r="BV59" s="9"/>
-      <c r="BW59" s="8"/>
-      <c r="BX59" s="7"/>
+      <c r="BW59" s="8">
+        <v>203</v>
+      </c>
+      <c r="BX59" s="7">
+        <v>937608</v>
+      </c>
       <c r="BY59" s="27">
         <f t="shared" si="32"/>
-        <v>-226</v>
+        <v>-23</v>
       </c>
       <c r="BZ59" s="28">
         <f t="shared" si="21"/>
-        <v>-1146679.9999990901</v>
+        <v>-209071.9999990901</v>
       </c>
       <c r="CA59" s="29">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>-0.18232811246315972</v>
       </c>
       <c r="CC59" s="9" t="s">
         <v>1</v>
@@ -15600,15 +15839,15 @@
       <c r="CF59" s="51"/>
       <c r="CG59" s="27">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-203</v>
       </c>
       <c r="CH59" s="28">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI59" s="29" t="e">
+        <v>-937608</v>
+      </c>
+      <c r="CI59" s="29">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK59" s="9" t="s">
         <v>1</v>
@@ -15841,19 +16080,23 @@
         <v>0</v>
       </c>
       <c r="BV60" s="4"/>
-      <c r="BW60" s="3"/>
-      <c r="BX60" s="2"/>
+      <c r="BW60" s="3">
+        <v>1694</v>
+      </c>
+      <c r="BX60" s="2">
+        <v>11194351</v>
+      </c>
       <c r="BY60" s="6">
         <f t="shared" si="32"/>
-        <v>-1693</v>
+        <v>1</v>
       </c>
       <c r="BZ60" s="5">
         <f t="shared" si="21"/>
-        <v>-10316829.33332772</v>
+        <v>877521.66667228006</v>
       </c>
       <c r="CA60" s="30">
         <f t="shared" si="22"/>
-        <v>-1</v>
+        <v>8.5057301843456321E-2</v>
       </c>
       <c r="CC60" s="4" t="s">
         <v>0</v>
@@ -15863,15 +16106,15 @@
       <c r="CF60" s="2"/>
       <c r="CG60" s="6">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-1694</v>
       </c>
       <c r="CH60" s="5">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="CI60" s="30" t="e">
+        <v>-11194351</v>
+      </c>
+      <c r="CI60" s="30">
         <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CK60" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D1F727-1718-BF43-8B32-9F3868ABB800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D276FAE-236C-1449-9E4B-39236C4BB271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15640" yWindow="3220" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1914,10 +1914,13 @@
       <c r="BV6" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="BW6" s="15">
+        <v>7</v>
+      </c>
       <c r="BX6" s="33"/>
       <c r="BY6" s="10">
         <f t="shared" si="20"/>
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="BZ6" s="12">
         <f t="shared" si="21"/>
@@ -1934,7 +1937,7 @@
       <c r="CF6" s="33"/>
       <c r="CG6" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="CH6" s="12">
         <f t="shared" si="24"/>
@@ -4799,11 +4802,13 @@
       <c r="BV17" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="BW17" s="15"/>
+      <c r="BW17" s="15">
+        <v>2</v>
+      </c>
       <c r="BX17" s="33"/>
       <c r="BY17" s="10">
         <f t="shared" si="20"/>
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="BZ17" s="12">
         <f t="shared" si="21"/>
@@ -4821,7 +4826,7 @@
       <c r="CF17" s="33"/>
       <c r="CG17" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CH17" s="12">
         <f t="shared" si="24"/>
@@ -7688,11 +7693,13 @@
       <c r="BV28" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="BW28" s="15"/>
+      <c r="BW28" s="15">
+        <v>4</v>
+      </c>
       <c r="BX28" s="33"/>
       <c r="BY28" s="10">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BZ28" s="12">
         <f t="shared" si="21"/>
@@ -7710,7 +7717,7 @@
       <c r="CF28" s="33"/>
       <c r="CG28" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="CH28" s="12">
         <f t="shared" si="24"/>
@@ -10577,11 +10584,13 @@
       <c r="BV39" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="BW39" s="15"/>
+      <c r="BW39" s="15">
+        <v>1</v>
+      </c>
       <c r="BX39" s="33"/>
       <c r="BY39" s="10">
         <f t="shared" si="32"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BZ39" s="12">
         <f t="shared" si="21"/>
@@ -10599,7 +10608,7 @@
       <c r="CF39" s="33"/>
       <c r="CG39" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CH39" s="12">
         <f t="shared" si="24"/>
@@ -13442,11 +13451,13 @@
       <c r="BV50" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="BW50" s="15"/>
+      <c r="BW50" s="15">
+        <v>1</v>
+      </c>
       <c r="BX50" s="33"/>
       <c r="BY50" s="10">
         <f t="shared" si="32"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BZ50" s="12">
         <f t="shared" si="21"/>
@@ -13464,7 +13475,7 @@
       <c r="CF50" s="33"/>
       <c r="CG50" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CH50" s="12">
         <f t="shared" si="24"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D276FAE-236C-1449-9E4B-39236C4BB271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D410CDE-1F29-AA43-B257-751CAEED2528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15640" yWindow="3220" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="50">
   <si>
     <t>總計</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>08/30-09/05</t>
+  </si>
+  <si>
+    <t>26Q4W11</t>
+  </si>
+  <si>
+    <t>09/06-09/12</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1087,9 @@
       </c>
       <c r="BV1" s="26"/>
       <c r="BX1" s="25"/>
-      <c r="CC1" s="26"/>
+      <c r="CC1" s="26" t="s">
+        <v>48</v>
+      </c>
       <c r="CD1" s="26"/>
       <c r="CF1" s="25"/>
       <c r="CK1" s="26"/>
@@ -1155,6 +1163,9 @@
       <c r="BY2" s="21"/>
       <c r="BZ2" s="21"/>
       <c r="CA2" s="21"/>
+      <c r="CC2" s="20" t="s">
+        <v>49</v>
+      </c>
       <c r="CD2" s="21"/>
       <c r="CF2" s="21"/>
       <c r="CG2" s="21"/>
@@ -1390,16 +1401,16 @@
         <v>13</v>
       </c>
       <c r="CC4" s="19" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="CD4" s="19" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="CE4" s="18" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="CF4" s="17" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="CG4" s="16" t="s">
         <v>13</v>
@@ -1679,13 +1690,15 @@
         <v>75</v>
       </c>
       <c r="CD5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CE5" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CE5" s="15">
+        <v>7657</v>
+      </c>
       <c r="CF5" s="33"/>
       <c r="CG5" s="10">
         <f t="shared" ref="CG5:CG60" si="23">CE5-BW5</f>
-        <v>-5042</v>
+        <v>2615</v>
       </c>
       <c r="CH5" s="12">
         <f t="shared" ref="CH5:CH60" si="24">CF5-BX5</f>
@@ -1706,7 +1719,7 @@
       <c r="CN5" s="33"/>
       <c r="CO5" s="10">
         <f t="shared" ref="CO5:CO60" si="26">CM5-CE5</f>
-        <v>0</v>
+        <v>-7657</v>
       </c>
       <c r="CP5" s="12">
         <f t="shared" ref="CP5:CP60" si="27">CN5-CF5</f>
@@ -1932,7 +1945,7 @@
       </c>
       <c r="CC6" s="14"/>
       <c r="CD6" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CF6" s="33"/>
       <c r="CG6" s="10">
@@ -2197,18 +2210,23 @@
       <c r="CD7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF7" s="12"/>
+      <c r="CE7" s="10">
+        <v>142</v>
+      </c>
+      <c r="CF7" s="12">
+        <v>157770</v>
+      </c>
       <c r="CG7" s="10">
         <f t="shared" si="23"/>
-        <v>-198</v>
+        <v>-56</v>
       </c>
       <c r="CH7" s="12">
         <f t="shared" si="24"/>
-        <v>-205488</v>
+        <v>-47718</v>
       </c>
       <c r="CI7" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.23221793973370708</v>
       </c>
       <c r="CK7" s="14"/>
       <c r="CL7" s="13" t="s">
@@ -2217,15 +2235,15 @@
       <c r="CN7" s="12"/>
       <c r="CO7" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-142</v>
       </c>
       <c r="CP7" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ7" s="11" t="e">
+        <v>-157770</v>
+      </c>
+      <c r="CQ7" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS7" s="14"/>
       <c r="CT7" s="13" t="s">
@@ -2460,18 +2478,23 @@
       <c r="CD8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF8" s="12"/>
+      <c r="CE8" s="10">
+        <v>229</v>
+      </c>
+      <c r="CF8" s="12">
+        <v>258686</v>
+      </c>
       <c r="CG8" s="10">
         <f t="shared" si="23"/>
-        <v>-204</v>
+        <v>25</v>
       </c>
       <c r="CH8" s="12">
         <f t="shared" si="24"/>
-        <v>-339810</v>
+        <v>-81124</v>
       </c>
       <c r="CI8" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.23873340984667904</v>
       </c>
       <c r="CK8" s="14"/>
       <c r="CL8" s="13" t="s">
@@ -2480,15 +2503,15 @@
       <c r="CN8" s="12"/>
       <c r="CO8" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-229</v>
       </c>
       <c r="CP8" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ8" s="11" t="e">
+        <v>-258686</v>
+      </c>
+      <c r="CQ8" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS8" s="14"/>
       <c r="CT8" s="13" t="s">
@@ -2723,18 +2746,23 @@
       <c r="CD9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF9" s="12"/>
+      <c r="CE9" s="10">
+        <v>37</v>
+      </c>
+      <c r="CF9" s="12">
+        <v>265076</v>
+      </c>
       <c r="CG9" s="10">
         <f t="shared" si="23"/>
-        <v>-57</v>
+        <v>-20</v>
       </c>
       <c r="CH9" s="12">
         <f t="shared" si="24"/>
-        <v>-396124</v>
+        <v>-131048</v>
       </c>
       <c r="CI9" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.33082570104310771</v>
       </c>
       <c r="CK9" s="14"/>
       <c r="CL9" s="13" t="s">
@@ -2743,15 +2771,15 @@
       <c r="CN9" s="12"/>
       <c r="CO9" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-37</v>
       </c>
       <c r="CP9" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ9" s="11" t="e">
+        <v>-265076</v>
+      </c>
+      <c r="CQ9" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS9" s="14"/>
       <c r="CT9" s="13" t="s">
@@ -2986,7 +3014,12 @@
       <c r="CD10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CF10" s="12"/>
+      <c r="CE10" s="10">
+        <v>0</v>
+      </c>
+      <c r="CF10" s="12">
+        <v>0</v>
+      </c>
       <c r="CG10" s="10">
         <f t="shared" si="23"/>
         <v>-59</v>
@@ -3249,18 +3282,23 @@
       <c r="CD11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CF11" s="12"/>
+      <c r="CE11" s="10">
+        <v>5</v>
+      </c>
+      <c r="CF11" s="12">
+        <v>40850</v>
+      </c>
       <c r="CG11" s="10">
         <f t="shared" si="23"/>
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="CH11" s="12">
         <f t="shared" si="24"/>
-        <v>-32240</v>
+        <v>8610</v>
       </c>
       <c r="CI11" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.26705955334987591</v>
       </c>
       <c r="CK11" s="14"/>
       <c r="CL11" s="13" t="s">
@@ -3269,15 +3307,15 @@
       <c r="CN11" s="12"/>
       <c r="CO11" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CP11" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ11" s="11" t="e">
+        <v>-40850</v>
+      </c>
+      <c r="CQ11" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS11" s="14"/>
       <c r="CT11" s="13" t="s">
@@ -3512,18 +3550,23 @@
       <c r="CD12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CF12" s="12"/>
+      <c r="CE12" s="10">
+        <v>22</v>
+      </c>
+      <c r="CF12" s="12">
+        <v>972138</v>
+      </c>
       <c r="CG12" s="10">
         <f t="shared" si="23"/>
-        <v>-29</v>
+        <v>-7</v>
       </c>
       <c r="CH12" s="12">
         <f t="shared" si="24"/>
-        <v>-1151102</v>
+        <v>-178964</v>
       </c>
       <c r="CI12" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.15547188693964567</v>
       </c>
       <c r="CK12" s="14"/>
       <c r="CL12" s="13" t="s">
@@ -3532,15 +3575,15 @@
       <c r="CN12" s="12"/>
       <c r="CO12" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="CP12" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ12" s="11" t="e">
+        <v>-972138</v>
+      </c>
+      <c r="CQ12" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS12" s="14"/>
       <c r="CT12" s="13" t="s">
@@ -3775,18 +3818,23 @@
       <c r="CD13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CF13" s="12"/>
+      <c r="CE13" s="10">
+        <v>46</v>
+      </c>
+      <c r="CF13" s="12">
+        <v>988381</v>
+      </c>
       <c r="CG13" s="10">
         <f t="shared" si="23"/>
-        <v>-49</v>
+        <v>-3</v>
       </c>
       <c r="CH13" s="12">
         <f t="shared" si="24"/>
-        <v>-1278952</v>
+        <v>-290571</v>
       </c>
       <c r="CI13" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.22719460933639418</v>
       </c>
       <c r="CK13" s="14"/>
       <c r="CL13" s="13" t="s">
@@ -3795,15 +3843,15 @@
       <c r="CN13" s="12"/>
       <c r="CO13" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="CP13" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ13" s="11" t="e">
+        <v>-988381</v>
+      </c>
+      <c r="CQ13" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS13" s="14"/>
       <c r="CT13" s="13" t="s">
@@ -4038,18 +4086,23 @@
       <c r="CD14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CF14" s="12"/>
+      <c r="CE14" s="10">
+        <v>26</v>
+      </c>
+      <c r="CF14" s="12">
+        <v>929905</v>
+      </c>
       <c r="CG14" s="10">
         <f t="shared" si="23"/>
-        <v>-40</v>
+        <v>-14</v>
       </c>
       <c r="CH14" s="12">
         <f t="shared" si="24"/>
-        <v>-1330476</v>
+        <v>-400571</v>
       </c>
       <c r="CI14" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.30107345040421624</v>
       </c>
       <c r="CK14" s="14"/>
       <c r="CL14" s="13" t="s">
@@ -4058,15 +4111,15 @@
       <c r="CN14" s="12"/>
       <c r="CO14" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="CP14" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ14" s="11" t="e">
+        <v>-929905</v>
+      </c>
+      <c r="CQ14" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS14" s="14"/>
       <c r="CT14" s="13" t="s">
@@ -4299,22 +4352,26 @@
         <v>0.33785096499636413</v>
       </c>
       <c r="CC15" s="9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="CD15" s="9"/>
-      <c r="CE15" s="8"/>
-      <c r="CF15" s="7"/>
+      <c r="CE15" s="8">
+        <v>507</v>
+      </c>
+      <c r="CF15" s="7">
+        <v>3612806</v>
+      </c>
       <c r="CG15" s="27">
         <f t="shared" si="23"/>
-        <v>-642</v>
+        <v>-135</v>
       </c>
       <c r="CH15" s="28">
         <f t="shared" si="24"/>
-        <v>-5229525</v>
+        <v>-1616719</v>
       </c>
       <c r="CI15" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.30915216965211945</v>
       </c>
       <c r="CK15" s="9" t="s">
         <v>18</v>
@@ -4324,15 +4381,15 @@
       <c r="CN15" s="7"/>
       <c r="CO15" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-507</v>
       </c>
       <c r="CP15" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ15" s="29" t="e">
+        <v>-3612806</v>
+      </c>
+      <c r="CQ15" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS15" s="9" t="s">
         <v>18</v>
@@ -4569,13 +4626,15 @@
         <v>76</v>
       </c>
       <c r="CD16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CE16" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CE16" s="15">
+        <v>6869</v>
+      </c>
       <c r="CF16" s="33"/>
       <c r="CG16" s="10">
         <f t="shared" si="23"/>
-        <v>-3854</v>
+        <v>3015</v>
       </c>
       <c r="CH16" s="12">
         <f t="shared" si="24"/>
@@ -4595,7 +4654,7 @@
       <c r="CN16" s="33"/>
       <c r="CO16" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-6869</v>
       </c>
       <c r="CP16" s="12">
         <f t="shared" si="27"/>
@@ -4820,7 +4879,7 @@
       </c>
       <c r="CC17" s="14"/>
       <c r="CD17" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CE17" s="15"/>
       <c r="CF17" s="33"/>
@@ -5088,18 +5147,23 @@
       <c r="CD18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF18" s="12"/>
+      <c r="CE18" s="10">
+        <v>139</v>
+      </c>
+      <c r="CF18" s="12">
+        <v>156901</v>
+      </c>
       <c r="CG18" s="10">
         <f t="shared" si="23"/>
-        <v>-139</v>
+        <v>0</v>
       </c>
       <c r="CH18" s="12">
         <f t="shared" si="24"/>
-        <v>-140534</v>
+        <v>16367</v>
       </c>
       <c r="CI18" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.11646292000512332</v>
       </c>
       <c r="CK18" s="14"/>
       <c r="CL18" s="13" t="s">
@@ -5108,15 +5172,15 @@
       <c r="CN18" s="12"/>
       <c r="CO18" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-139</v>
       </c>
       <c r="CP18" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ18" s="11" t="e">
+        <v>-156901</v>
+      </c>
+      <c r="CQ18" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS18" s="14"/>
       <c r="CT18" s="13" t="s">
@@ -5351,18 +5415,23 @@
       <c r="CD19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF19" s="12"/>
+      <c r="CE19" s="10">
+        <v>245</v>
+      </c>
+      <c r="CF19" s="12">
+        <v>238287</v>
+      </c>
       <c r="CG19" s="10">
         <f t="shared" si="23"/>
-        <v>-183</v>
+        <v>62</v>
       </c>
       <c r="CH19" s="12">
         <f t="shared" si="24"/>
-        <v>-189429</v>
+        <v>48858</v>
       </c>
       <c r="CI19" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.25792249338802403</v>
       </c>
       <c r="CK19" s="14"/>
       <c r="CL19" s="13" t="s">
@@ -5371,15 +5440,15 @@
       <c r="CN19" s="12"/>
       <c r="CO19" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-245</v>
       </c>
       <c r="CP19" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ19" s="11" t="e">
+        <v>-238287</v>
+      </c>
+      <c r="CQ19" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS19" s="14"/>
       <c r="CT19" s="13" t="s">
@@ -5614,18 +5683,23 @@
       <c r="CD20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF20" s="12"/>
+      <c r="CE20" s="10">
+        <v>33</v>
+      </c>
+      <c r="CF20" s="12">
+        <v>232638</v>
+      </c>
       <c r="CG20" s="10">
         <f t="shared" si="23"/>
-        <v>-23</v>
+        <v>10</v>
       </c>
       <c r="CH20" s="12">
         <f t="shared" si="24"/>
-        <v>-131210</v>
+        <v>101428</v>
       </c>
       <c r="CI20" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.77302034905876071</v>
       </c>
       <c r="CK20" s="14"/>
       <c r="CL20" s="13" t="s">
@@ -5634,15 +5708,15 @@
       <c r="CN20" s="12"/>
       <c r="CO20" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="CP20" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ20" s="11" t="e">
+        <v>-232638</v>
+      </c>
+      <c r="CQ20" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS20" s="14"/>
       <c r="CT20" s="13" t="s">
@@ -5877,18 +5951,23 @@
       <c r="CD21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CF21" s="12"/>
+      <c r="CE21" s="10">
+        <v>1</v>
+      </c>
+      <c r="CF21" s="12">
+        <v>13238</v>
+      </c>
       <c r="CG21" s="10">
         <f t="shared" si="23"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CH21" s="12">
         <f t="shared" si="24"/>
-        <v>-7524</v>
+        <v>5714</v>
       </c>
       <c r="CI21" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.7594364699627858</v>
       </c>
       <c r="CK21" s="14"/>
       <c r="CL21" s="13" t="s">
@@ -5897,15 +5976,15 @@
       <c r="CN21" s="12"/>
       <c r="CO21" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP21" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ21" s="11" t="e">
+        <v>-13238</v>
+      </c>
+      <c r="CQ21" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS21" s="14"/>
       <c r="CT21" s="13" t="s">
@@ -6140,18 +6219,23 @@
       <c r="CD22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CF22" s="12"/>
+      <c r="CE22" s="10">
+        <v>18</v>
+      </c>
+      <c r="CF22" s="12">
+        <v>90450</v>
+      </c>
       <c r="CG22" s="10">
         <f t="shared" si="23"/>
-        <v>-12</v>
+        <v>6</v>
       </c>
       <c r="CH22" s="12">
         <f t="shared" si="24"/>
-        <v>-67380</v>
+        <v>23070</v>
       </c>
       <c r="CI22" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.34238646482635798</v>
       </c>
       <c r="CK22" s="14"/>
       <c r="CL22" s="13" t="s">
@@ -6160,15 +6244,15 @@
       <c r="CN22" s="12"/>
       <c r="CO22" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="CP22" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ22" s="11" t="e">
+        <v>-90450</v>
+      </c>
+      <c r="CQ22" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS22" s="14"/>
       <c r="CT22" s="13" t="s">
@@ -6403,18 +6487,23 @@
       <c r="CD23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CF23" s="12"/>
+      <c r="CE23" s="10">
+        <v>24</v>
+      </c>
+      <c r="CF23" s="12">
+        <v>838090</v>
+      </c>
       <c r="CG23" s="10">
         <f t="shared" si="23"/>
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="CH23" s="12">
         <f t="shared" si="24"/>
-        <v>-731464</v>
+        <v>106626</v>
       </c>
       <c r="CI23" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.14577067360799711</v>
       </c>
       <c r="CK23" s="14"/>
       <c r="CL23" s="13" t="s">
@@ -6423,15 +6512,15 @@
       <c r="CN23" s="12"/>
       <c r="CO23" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="CP23" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ23" s="11" t="e">
+        <v>-838090</v>
+      </c>
+      <c r="CQ23" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS23" s="14"/>
       <c r="CT23" s="13" t="s">
@@ -6666,18 +6755,23 @@
       <c r="CD24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CF24" s="12"/>
+      <c r="CE24" s="10">
+        <v>61</v>
+      </c>
+      <c r="CF24" s="12">
+        <v>1395048</v>
+      </c>
       <c r="CG24" s="10">
         <f t="shared" si="23"/>
-        <v>-28</v>
+        <v>33</v>
       </c>
       <c r="CH24" s="12">
         <f t="shared" si="24"/>
-        <v>-737238</v>
+        <v>657810</v>
       </c>
       <c r="CI24" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.89226274283202978</v>
       </c>
       <c r="CK24" s="14"/>
       <c r="CL24" s="13" t="s">
@@ -6686,15 +6780,15 @@
       <c r="CN24" s="12"/>
       <c r="CO24" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-61</v>
       </c>
       <c r="CP24" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ24" s="11" t="e">
+        <v>-1395048</v>
+      </c>
+      <c r="CQ24" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS24" s="14"/>
       <c r="CT24" s="13" t="s">
@@ -6929,18 +7023,23 @@
       <c r="CD25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CF25" s="12"/>
+      <c r="CE25" s="10">
+        <v>54</v>
+      </c>
+      <c r="CF25" s="12">
+        <v>1783098</v>
+      </c>
       <c r="CG25" s="10">
         <f t="shared" si="23"/>
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="CH25" s="12">
         <f t="shared" si="24"/>
-        <v>-927717</v>
+        <v>855381</v>
       </c>
       <c r="CI25" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.92202794602233229</v>
       </c>
       <c r="CK25" s="14"/>
       <c r="CL25" s="13" t="s">
@@ -6949,15 +7048,15 @@
       <c r="CN25" s="12"/>
       <c r="CO25" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="CP25" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ25" s="11" t="e">
+        <v>-1783098</v>
+      </c>
+      <c r="CQ25" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS25" s="14"/>
       <c r="CT25" s="13" t="s">
@@ -7193,19 +7292,23 @@
         <v>12</v>
       </c>
       <c r="CD26" s="9"/>
-      <c r="CE26" s="8"/>
-      <c r="CF26" s="7"/>
+      <c r="CE26" s="8">
+        <v>575</v>
+      </c>
+      <c r="CF26" s="7">
+        <v>4747750</v>
+      </c>
       <c r="CG26" s="27">
         <f t="shared" si="23"/>
-        <v>-437</v>
+        <v>138</v>
       </c>
       <c r="CH26" s="28">
         <f t="shared" si="24"/>
-        <v>-2932496</v>
+        <v>1815254</v>
       </c>
       <c r="CI26" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.61901329106672265</v>
       </c>
       <c r="CK26" s="9" t="s">
         <v>12</v>
@@ -7215,15 +7318,15 @@
       <c r="CN26" s="7"/>
       <c r="CO26" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-575</v>
       </c>
       <c r="CP26" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ26" s="29" t="e">
+        <v>-4747750</v>
+      </c>
+      <c r="CQ26" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS26" s="9" t="s">
         <v>12</v>
@@ -7460,13 +7563,15 @@
         <v>77</v>
       </c>
       <c r="CD27" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CE27" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CE27" s="15">
+        <v>4471</v>
+      </c>
       <c r="CF27" s="33"/>
       <c r="CG27" s="10">
         <f t="shared" si="23"/>
-        <v>-2744</v>
+        <v>1727</v>
       </c>
       <c r="CH27" s="12">
         <f t="shared" si="24"/>
@@ -7486,7 +7591,7 @@
       <c r="CN27" s="33"/>
       <c r="CO27" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-4471</v>
       </c>
       <c r="CP27" s="12">
         <f t="shared" si="27"/>
@@ -7711,7 +7816,7 @@
       </c>
       <c r="CC28" s="14"/>
       <c r="CD28" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CE28" s="15"/>
       <c r="CF28" s="33"/>
@@ -7979,18 +8084,23 @@
       <c r="CD29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF29" s="12"/>
+      <c r="CE29" s="10">
+        <v>56</v>
+      </c>
+      <c r="CF29" s="12">
+        <v>55918</v>
+      </c>
       <c r="CG29" s="10">
         <f t="shared" si="23"/>
-        <v>-86</v>
+        <v>-30</v>
       </c>
       <c r="CH29" s="12">
         <f t="shared" si="24"/>
-        <v>-95122</v>
+        <v>-39204</v>
       </c>
       <c r="CI29" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.41214440402851077</v>
       </c>
       <c r="CK29" s="14"/>
       <c r="CL29" s="13" t="s">
@@ -7999,15 +8109,15 @@
       <c r="CN29" s="12"/>
       <c r="CO29" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-56</v>
       </c>
       <c r="CP29" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ29" s="11" t="e">
+        <v>-55918</v>
+      </c>
+      <c r="CQ29" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS29" s="14"/>
       <c r="CT29" s="13" t="s">
@@ -8242,18 +8352,23 @@
       <c r="CD30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF30" s="12"/>
+      <c r="CE30" s="10">
+        <v>77</v>
+      </c>
+      <c r="CF30" s="12">
+        <v>71239</v>
+      </c>
       <c r="CG30" s="10">
         <f t="shared" si="23"/>
-        <v>-61</v>
+        <v>16</v>
       </c>
       <c r="CH30" s="12">
         <f t="shared" si="24"/>
-        <v>-52987</v>
+        <v>18252</v>
       </c>
       <c r="CI30" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.34446184913280614</v>
       </c>
       <c r="CK30" s="14"/>
       <c r="CL30" s="13" t="s">
@@ -8262,15 +8377,15 @@
       <c r="CN30" s="12"/>
       <c r="CO30" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-77</v>
       </c>
       <c r="CP30" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ30" s="11" t="e">
+        <v>-71239</v>
+      </c>
+      <c r="CQ30" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS30" s="14"/>
       <c r="CT30" s="13" t="s">
@@ -8505,18 +8620,23 @@
       <c r="CD31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF31" s="12"/>
+      <c r="CE31" s="10">
+        <v>13</v>
+      </c>
+      <c r="CF31" s="12">
+        <v>84733</v>
+      </c>
       <c r="CG31" s="10">
         <f t="shared" si="23"/>
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="CH31" s="12">
         <f t="shared" si="24"/>
-        <v>-102048</v>
+        <v>-17315</v>
       </c>
       <c r="CI31" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.16967505487613671</v>
       </c>
       <c r="CK31" s="14"/>
       <c r="CL31" s="13" t="s">
@@ -8525,15 +8645,15 @@
       <c r="CN31" s="12"/>
       <c r="CO31" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CP31" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ31" s="11" t="e">
+        <v>-84733</v>
+      </c>
+      <c r="CQ31" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS31" s="14"/>
       <c r="CT31" s="13" t="s">
@@ -8768,18 +8888,23 @@
       <c r="CD32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CF32" s="12"/>
+      <c r="CE32" s="10">
+        <v>1</v>
+      </c>
+      <c r="CF32" s="12">
+        <v>7524</v>
+      </c>
       <c r="CG32" s="10">
         <f t="shared" si="23"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="CH32" s="12">
         <f t="shared" si="24"/>
-        <v>-27333</v>
+        <v>-19809</v>
       </c>
       <c r="CI32" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.72472835034573591</v>
       </c>
       <c r="CK32" s="14"/>
       <c r="CL32" s="13" t="s">
@@ -8788,15 +8913,15 @@
       <c r="CN32" s="12"/>
       <c r="CO32" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP32" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ32" s="11" t="e">
+        <v>-7524</v>
+      </c>
+      <c r="CQ32" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS32" s="14"/>
       <c r="CT32" s="13" t="s">
@@ -9031,14 +9156,19 @@
       <c r="CD33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CF33" s="12"/>
+      <c r="CE33" s="10">
+        <v>5</v>
+      </c>
+      <c r="CF33" s="12">
+        <v>20650</v>
+      </c>
       <c r="CG33" s="10">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CH33" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>20650</v>
       </c>
       <c r="CI33" s="11" t="e">
         <f t="shared" si="25"/>
@@ -9051,15 +9181,15 @@
       <c r="CN33" s="12"/>
       <c r="CO33" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CP33" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ33" s="11" t="e">
+        <v>-20650</v>
+      </c>
+      <c r="CQ33" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS33" s="14"/>
       <c r="CT33" s="13" t="s">
@@ -9294,18 +9424,23 @@
       <c r="CD34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CF34" s="12"/>
+      <c r="CE34" s="10">
+        <v>4</v>
+      </c>
+      <c r="CF34" s="12">
+        <v>116713</v>
+      </c>
       <c r="CG34" s="10">
         <f t="shared" si="23"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="CH34" s="12">
         <f t="shared" si="24"/>
-        <v>-173517</v>
+        <v>-56804</v>
       </c>
       <c r="CI34" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.32736849991643469</v>
       </c>
       <c r="CK34" s="14"/>
       <c r="CL34" s="13" t="s">
@@ -9314,15 +9449,15 @@
       <c r="CN34" s="12"/>
       <c r="CO34" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="CP34" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ34" s="11" t="e">
+        <v>-116713</v>
+      </c>
+      <c r="CQ34" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS34" s="14"/>
       <c r="CT34" s="13" t="s">
@@ -9557,18 +9692,23 @@
       <c r="CD35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CF35" s="12"/>
+      <c r="CE35" s="10">
+        <v>9</v>
+      </c>
+      <c r="CF35" s="12">
+        <v>247714</v>
+      </c>
       <c r="CG35" s="10">
         <f t="shared" si="23"/>
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="CH35" s="12">
         <f t="shared" si="24"/>
-        <v>-121143</v>
+        <v>126571</v>
       </c>
       <c r="CI35" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>1.044806550935671</v>
       </c>
       <c r="CK35" s="14"/>
       <c r="CL35" s="13" t="s">
@@ -9577,15 +9717,15 @@
       <c r="CN35" s="12"/>
       <c r="CO35" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="CP35" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ35" s="11" t="e">
+        <v>-247714</v>
+      </c>
+      <c r="CQ35" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS35" s="14"/>
       <c r="CT35" s="13" t="s">
@@ -9820,18 +9960,23 @@
       <c r="CD36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CF36" s="12"/>
+      <c r="CE36" s="10">
+        <v>4</v>
+      </c>
+      <c r="CF36" s="12">
+        <v>142476</v>
+      </c>
       <c r="CG36" s="10">
         <f t="shared" si="23"/>
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="CH36" s="12">
         <f t="shared" si="24"/>
-        <v>-324290</v>
+        <v>-181814</v>
       </c>
       <c r="CI36" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.56065250238983622</v>
       </c>
       <c r="CK36" s="14"/>
       <c r="CL36" s="13" t="s">
@@ -9840,15 +9985,15 @@
       <c r="CN36" s="12"/>
       <c r="CO36" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="CP36" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ36" s="11" t="e">
+        <v>-142476</v>
+      </c>
+      <c r="CQ36" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS36" s="14"/>
       <c r="CT36" s="13" t="s">
@@ -10084,19 +10229,23 @@
         <v>11</v>
       </c>
       <c r="CD37" s="9"/>
-      <c r="CE37" s="8"/>
-      <c r="CF37" s="7"/>
+      <c r="CE37" s="8">
+        <v>169</v>
+      </c>
+      <c r="CF37" s="7">
+        <v>746967</v>
+      </c>
       <c r="CG37" s="27">
         <f t="shared" si="23"/>
-        <v>-187</v>
+        <v>-18</v>
       </c>
       <c r="CH37" s="28">
         <f t="shared" si="24"/>
-        <v>-896440</v>
+        <v>-149473</v>
       </c>
       <c r="CI37" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.16674066306724378</v>
       </c>
       <c r="CK37" s="9" t="s">
         <v>11</v>
@@ -10106,15 +10255,15 @@
       <c r="CN37" s="7"/>
       <c r="CO37" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-169</v>
       </c>
       <c r="CP37" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ37" s="29" t="e">
+        <v>-746967</v>
+      </c>
+      <c r="CQ37" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS37" s="9" t="s">
         <v>11</v>
@@ -10351,13 +10500,15 @@
         <v>81</v>
       </c>
       <c r="CD38" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CE38" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CE38" s="15">
+        <v>2314</v>
+      </c>
       <c r="CF38" s="33"/>
       <c r="CG38" s="10">
         <f t="shared" si="23"/>
-        <v>-1732</v>
+        <v>582</v>
       </c>
       <c r="CH38" s="12">
         <f t="shared" si="24"/>
@@ -10377,7 +10528,7 @@
       <c r="CN38" s="33"/>
       <c r="CO38" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-2314</v>
       </c>
       <c r="CP38" s="12">
         <f t="shared" si="27"/>
@@ -10602,7 +10753,7 @@
       </c>
       <c r="CC39" s="14"/>
       <c r="CD39" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CE39" s="15"/>
       <c r="CF39" s="33"/>
@@ -10870,18 +11021,23 @@
       <c r="CD40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF40" s="12"/>
+      <c r="CE40" s="10">
+        <v>105</v>
+      </c>
+      <c r="CF40" s="12">
+        <v>99201</v>
+      </c>
       <c r="CG40" s="10">
         <f t="shared" si="23"/>
-        <v>-79</v>
+        <v>26</v>
       </c>
       <c r="CH40" s="12">
         <f t="shared" si="24"/>
-        <v>-66290</v>
+        <v>32911</v>
       </c>
       <c r="CI40" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.49647005581535675</v>
       </c>
       <c r="CK40" s="14"/>
       <c r="CL40" s="13" t="s">
@@ -10890,15 +11046,15 @@
       <c r="CN40" s="12"/>
       <c r="CO40" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-105</v>
       </c>
       <c r="CP40" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ40" s="11" t="e">
+        <v>-99201</v>
+      </c>
+      <c r="CQ40" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS40" s="14"/>
       <c r="CT40" s="13" t="s">
@@ -11133,18 +11289,23 @@
       <c r="CD41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF41" s="12"/>
+      <c r="CE41" s="10">
+        <v>103</v>
+      </c>
+      <c r="CF41" s="12">
+        <v>116981</v>
+      </c>
       <c r="CG41" s="10">
         <f t="shared" si="23"/>
-        <v>-98</v>
+        <v>5</v>
       </c>
       <c r="CH41" s="12">
         <f t="shared" si="24"/>
-        <v>-87552</v>
+        <v>29429</v>
       </c>
       <c r="CI41" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.33613167032163743</v>
       </c>
       <c r="CK41" s="14"/>
       <c r="CL41" s="13" t="s">
@@ -11153,15 +11314,15 @@
       <c r="CN41" s="12"/>
       <c r="CO41" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-103</v>
       </c>
       <c r="CP41" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ41" s="11" t="e">
+        <v>-116981</v>
+      </c>
+      <c r="CQ41" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS41" s="14"/>
       <c r="CT41" s="13" t="s">
@@ -11396,18 +11557,23 @@
       <c r="CD42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF42" s="12"/>
+      <c r="CE42" s="10">
+        <v>10</v>
+      </c>
+      <c r="CF42" s="12">
+        <v>75905</v>
+      </c>
       <c r="CG42" s="10">
         <f t="shared" si="23"/>
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="CH42" s="12">
         <f t="shared" si="24"/>
-        <v>-61324</v>
+        <v>14581</v>
       </c>
       <c r="CI42" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.23776987802491684</v>
       </c>
       <c r="CK42" s="14"/>
       <c r="CL42" s="13" t="s">
@@ -11416,15 +11582,15 @@
       <c r="CN42" s="12"/>
       <c r="CO42" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="CP42" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ42" s="11" t="e">
+        <v>-75905</v>
+      </c>
+      <c r="CQ42" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS42" s="14"/>
       <c r="CT42" s="13" t="s">
@@ -11659,18 +11825,23 @@
       <c r="CD43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CF43" s="12"/>
+      <c r="CE43" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF43" s="12">
+        <v>15048</v>
+      </c>
       <c r="CG43" s="10">
         <f t="shared" si="23"/>
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="CH43" s="12">
         <f t="shared" si="24"/>
-        <v>-27333</v>
+        <v>-12285</v>
       </c>
       <c r="CI43" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.44945670069147187</v>
       </c>
       <c r="CK43" s="14"/>
       <c r="CL43" s="13" t="s">
@@ -11679,15 +11850,15 @@
       <c r="CN43" s="12"/>
       <c r="CO43" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CP43" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ43" s="11" t="e">
+        <v>-15048</v>
+      </c>
+      <c r="CQ43" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS43" s="14"/>
       <c r="CT43" s="13" t="s">
@@ -11922,19 +12093,23 @@
       <c r="CD44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CE44" s="50"/>
-      <c r="CF44" s="50"/>
+      <c r="CE44" s="50">
+        <v>1</v>
+      </c>
+      <c r="CF44" s="50">
+        <v>6990</v>
+      </c>
       <c r="CG44" s="10">
         <f t="shared" si="23"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CH44" s="12">
         <f t="shared" si="24"/>
-        <v>-10680</v>
+        <v>-3690</v>
       </c>
       <c r="CI44" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.3455056179775281</v>
       </c>
       <c r="CK44" s="14"/>
       <c r="CL44" s="13" t="s">
@@ -11943,15 +12118,15 @@
       <c r="CN44" s="12"/>
       <c r="CO44" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP44" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ44" s="11" t="e">
+        <v>-6990</v>
+      </c>
+      <c r="CQ44" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS44" s="14"/>
       <c r="CT44" s="13" t="s">
@@ -12186,19 +12361,23 @@
       <c r="CD45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CE45" s="50"/>
-      <c r="CF45" s="50"/>
+      <c r="CE45" s="50">
+        <v>4</v>
+      </c>
+      <c r="CF45" s="50">
+        <v>112952</v>
+      </c>
       <c r="CG45" s="10">
         <f t="shared" si="23"/>
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="CH45" s="12">
         <f t="shared" si="24"/>
-        <v>-258722</v>
+        <v>-145770</v>
       </c>
       <c r="CI45" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.56342328831718991</v>
       </c>
       <c r="CK45" s="14"/>
       <c r="CL45" s="13" t="s">
@@ -12207,15 +12386,15 @@
       <c r="CN45" s="12"/>
       <c r="CO45" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="CP45" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ45" s="11" t="e">
+        <v>-112952</v>
+      </c>
+      <c r="CQ45" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS45" s="14"/>
       <c r="CT45" s="13" t="s">
@@ -12450,19 +12629,23 @@
       <c r="CD46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CE46" s="50"/>
-      <c r="CF46" s="50"/>
+      <c r="CE46" s="50">
+        <v>24</v>
+      </c>
+      <c r="CF46" s="50">
+        <v>543524</v>
+      </c>
       <c r="CG46" s="10">
         <f t="shared" si="23"/>
-        <v>-9</v>
+        <v>15</v>
       </c>
       <c r="CH46" s="12">
         <f t="shared" si="24"/>
-        <v>-187810</v>
+        <v>355714</v>
       </c>
       <c r="CI46" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>1.894009903626005</v>
       </c>
       <c r="CK46" s="14"/>
       <c r="CL46" s="13" t="s">
@@ -12471,15 +12654,15 @@
       <c r="CN46" s="12"/>
       <c r="CO46" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="CP46" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ46" s="11" t="e">
+        <v>-543524</v>
+      </c>
+      <c r="CQ46" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS46" s="14"/>
       <c r="CT46" s="13" t="s">
@@ -12714,19 +12897,23 @@
       <c r="CD47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CE47" s="50"/>
-      <c r="CF47" s="50"/>
+      <c r="CE47" s="50">
+        <v>10</v>
+      </c>
+      <c r="CF47" s="50">
+        <v>400000</v>
+      </c>
       <c r="CG47" s="10">
         <f t="shared" si="23"/>
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="CH47" s="12">
         <f t="shared" si="24"/>
-        <v>-498571</v>
+        <v>-98571</v>
       </c>
       <c r="CI47" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.19770704673958173</v>
       </c>
       <c r="CK47" s="14"/>
       <c r="CL47" s="13" t="s">
@@ -12735,15 +12922,15 @@
       <c r="CN47" s="12"/>
       <c r="CO47" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="CP47" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ47" s="11" t="e">
+        <v>-400000</v>
+      </c>
+      <c r="CQ47" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS47" s="14"/>
       <c r="CT47" s="13" t="s">
@@ -12979,19 +13166,23 @@
         <v>10</v>
       </c>
       <c r="CD48" s="9"/>
-      <c r="CE48" s="51"/>
-      <c r="CF48" s="51"/>
+      <c r="CE48" s="51">
+        <v>259</v>
+      </c>
+      <c r="CF48" s="51">
+        <v>1370601</v>
+      </c>
       <c r="CG48" s="27">
         <f t="shared" si="23"/>
-        <v>-225</v>
+        <v>34</v>
       </c>
       <c r="CH48" s="28">
         <f t="shared" si="24"/>
-        <v>-1198282</v>
+        <v>172319</v>
       </c>
       <c r="CI48" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.14380504755975637</v>
       </c>
       <c r="CK48" s="9" t="s">
         <v>10</v>
@@ -13001,15 +13192,15 @@
       <c r="CN48" s="7"/>
       <c r="CO48" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-259</v>
       </c>
       <c r="CP48" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ48" s="29" t="e">
+        <v>-1370601</v>
+      </c>
+      <c r="CQ48" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS48" s="9" t="s">
         <v>10</v>
@@ -13218,7 +13409,7 @@
         <v>84</v>
       </c>
       <c r="CD49" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CE49" s="15"/>
       <c r="CF49" s="33"/>
@@ -13469,7 +13660,7 @@
       </c>
       <c r="CC50" s="14"/>
       <c r="CD50" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CE50" s="15"/>
       <c r="CF50" s="33"/>
@@ -13737,18 +13928,23 @@
       <c r="CD51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CF51" s="12"/>
+      <c r="CE51" s="10">
+        <v>90</v>
+      </c>
+      <c r="CF51" s="12">
+        <v>89890</v>
+      </c>
       <c r="CG51" s="10">
         <f t="shared" si="23"/>
-        <v>-104</v>
+        <v>-14</v>
       </c>
       <c r="CH51" s="12">
         <f t="shared" si="24"/>
-        <v>-95841</v>
+        <v>-5951</v>
       </c>
       <c r="CI51" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-6.2092423910434992E-2</v>
       </c>
       <c r="CK51" s="14"/>
       <c r="CL51" s="13" t="s">
@@ -13757,15 +13953,15 @@
       <c r="CN51" s="12"/>
       <c r="CO51" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="CP51" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ51" s="11" t="e">
+        <v>-89890</v>
+      </c>
+      <c r="CQ51" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS51" s="14"/>
       <c r="CT51" s="13" t="s">
@@ -14000,18 +14196,23 @@
       <c r="CD52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CF52" s="12"/>
+      <c r="CE52" s="10">
+        <v>77</v>
+      </c>
+      <c r="CF52" s="12">
+        <v>75171</v>
+      </c>
       <c r="CG52" s="10">
         <f t="shared" si="23"/>
-        <v>-63</v>
+        <v>14</v>
       </c>
       <c r="CH52" s="12">
         <f t="shared" si="24"/>
-        <v>-89305</v>
+        <v>-14134</v>
       </c>
       <c r="CI52" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.15826661441128717</v>
       </c>
       <c r="CK52" s="14"/>
       <c r="CL52" s="13" t="s">
@@ -14020,15 +14221,15 @@
       <c r="CN52" s="12"/>
       <c r="CO52" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-77</v>
       </c>
       <c r="CP52" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ52" s="11" t="e">
+        <v>-75171</v>
+      </c>
+      <c r="CQ52" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS52" s="14"/>
       <c r="CT52" s="13" t="s">
@@ -14263,18 +14464,23 @@
       <c r="CD53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CF53" s="12"/>
+      <c r="CE53" s="10">
+        <v>13</v>
+      </c>
+      <c r="CF53" s="12">
+        <v>103781</v>
+      </c>
       <c r="CG53" s="10">
         <f t="shared" si="23"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="CH53" s="12">
         <f t="shared" si="24"/>
-        <v>-35657</v>
+        <v>68124</v>
       </c>
       <c r="CI53" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>1.9105365005468773</v>
       </c>
       <c r="CK53" s="14"/>
       <c r="CL53" s="13" t="s">
@@ -14283,15 +14489,15 @@
       <c r="CN53" s="12"/>
       <c r="CO53" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CP53" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ53" s="11" t="e">
+        <v>-103781</v>
+      </c>
+      <c r="CQ53" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS53" s="14"/>
       <c r="CT53" s="13" t="s">
@@ -14526,18 +14732,23 @@
       <c r="CD54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CF54" s="12"/>
+      <c r="CE54" s="10">
+        <v>1</v>
+      </c>
+      <c r="CF54" s="12">
+        <v>7524</v>
+      </c>
       <c r="CG54" s="10">
         <f t="shared" si="23"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CH54" s="12">
         <f t="shared" si="24"/>
-        <v>-15048</v>
+        <v>-7524</v>
       </c>
       <c r="CI54" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="CK54" s="14"/>
       <c r="CL54" s="13" t="s">
@@ -14546,15 +14757,15 @@
       <c r="CN54" s="12"/>
       <c r="CO54" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP54" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ54" s="11" t="e">
+        <v>-7524</v>
+      </c>
+      <c r="CQ54" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS54" s="14"/>
       <c r="CT54" s="13" t="s">
@@ -14789,19 +15000,23 @@
       <c r="CD55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CE55" s="50"/>
-      <c r="CF55" s="50"/>
+      <c r="CE55" s="50">
+        <v>3</v>
+      </c>
+      <c r="CF55" s="50">
+        <v>9970</v>
+      </c>
       <c r="CG55" s="10">
         <f t="shared" si="23"/>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="CH55" s="12">
         <f t="shared" si="24"/>
-        <v>-13770</v>
+        <v>-3800</v>
       </c>
       <c r="CI55" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.27596223674655046</v>
       </c>
       <c r="CK55" s="14"/>
       <c r="CL55" s="13" t="s">
@@ -14810,15 +15025,15 @@
       <c r="CN55" s="12"/>
       <c r="CO55" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="CP55" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ55" s="11" t="e">
+        <v>-9970</v>
+      </c>
+      <c r="CQ55" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS55" s="14"/>
       <c r="CT55" s="13" t="s">
@@ -15053,19 +15268,23 @@
       <c r="CD56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CE56" s="50"/>
-      <c r="CF56" s="50"/>
+      <c r="CE56" s="50">
+        <v>5</v>
+      </c>
+      <c r="CF56" s="50">
+        <v>139524</v>
+      </c>
       <c r="CG56" s="10">
         <f t="shared" si="23"/>
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="CH56" s="12">
         <f t="shared" si="24"/>
-        <v>-170368</v>
+        <v>-30844</v>
       </c>
       <c r="CI56" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>-0.18104338842975207</v>
       </c>
       <c r="CK56" s="14"/>
       <c r="CL56" s="13" t="s">
@@ -15074,15 +15293,15 @@
       <c r="CN56" s="12"/>
       <c r="CO56" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CP56" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ56" s="11" t="e">
+        <v>-139524</v>
+      </c>
+      <c r="CQ56" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS56" s="14"/>
       <c r="CT56" s="13" t="s">
@@ -15317,19 +15536,23 @@
       <c r="CD57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CE57" s="50"/>
-      <c r="CF57" s="50"/>
+      <c r="CE57" s="50">
+        <v>10</v>
+      </c>
+      <c r="CF57" s="50">
+        <v>218571</v>
+      </c>
       <c r="CG57" s="10">
         <f t="shared" si="23"/>
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="CH57" s="12">
         <f t="shared" si="24"/>
-        <v>-152095</v>
+        <v>66476</v>
       </c>
       <c r="CI57" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.43706893717742201</v>
       </c>
       <c r="CK57" s="14"/>
       <c r="CL57" s="13" t="s">
@@ -15338,15 +15561,15 @@
       <c r="CN57" s="12"/>
       <c r="CO57" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="CP57" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ57" s="11" t="e">
+        <v>-218571</v>
+      </c>
+      <c r="CQ57" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS57" s="14"/>
       <c r="CT57" s="13" t="s">
@@ -15581,19 +15804,23 @@
       <c r="CD58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CE58" s="50"/>
-      <c r="CF58" s="50"/>
+      <c r="CE58" s="50">
+        <v>12</v>
+      </c>
+      <c r="CF58" s="50">
+        <v>400672</v>
+      </c>
       <c r="CG58" s="10">
         <f t="shared" si="23"/>
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="CH58" s="12">
         <f t="shared" si="24"/>
-        <v>-365524</v>
+        <v>35148</v>
       </c>
       <c r="CI58" s="11">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>9.6157844628533287E-2</v>
       </c>
       <c r="CK58" s="14"/>
       <c r="CL58" s="13" t="s">
@@ -15602,15 +15829,15 @@
       <c r="CN58" s="12"/>
       <c r="CO58" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="CP58" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ58" s="11" t="e">
+        <v>-400672</v>
+      </c>
+      <c r="CQ58" s="11">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS58" s="14"/>
       <c r="CT58" s="13" t="s">
@@ -15846,19 +16073,23 @@
         <v>1</v>
       </c>
       <c r="CD59" s="9"/>
-      <c r="CE59" s="51"/>
-      <c r="CF59" s="51"/>
+      <c r="CE59" s="51">
+        <v>211</v>
+      </c>
+      <c r="CF59" s="51">
+        <v>1045103</v>
+      </c>
       <c r="CG59" s="27">
         <f t="shared" si="23"/>
-        <v>-203</v>
+        <v>8</v>
       </c>
       <c r="CH59" s="28">
         <f t="shared" si="24"/>
-        <v>-937608</v>
+        <v>107495</v>
       </c>
       <c r="CI59" s="29">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>0.1146481258692332</v>
       </c>
       <c r="CK59" s="9" t="s">
         <v>1</v>
@@ -15868,15 +16099,15 @@
       <c r="CN59" s="7"/>
       <c r="CO59" s="27">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-211</v>
       </c>
       <c r="CP59" s="28">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ59" s="29" t="e">
+        <v>-1045103</v>
+      </c>
+      <c r="CQ59" s="29">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS59" s="9" t="s">
         <v>1</v>
@@ -16113,19 +16344,23 @@
         <v>0</v>
       </c>
       <c r="CD60" s="4"/>
-      <c r="CE60" s="3"/>
-      <c r="CF60" s="2"/>
+      <c r="CE60" s="3">
+        <v>1721</v>
+      </c>
+      <c r="CF60" s="2">
+        <v>11523227</v>
+      </c>
       <c r="CG60" s="6">
         <f t="shared" si="23"/>
-        <v>-1694</v>
+        <v>27</v>
       </c>
       <c r="CH60" s="5">
         <f t="shared" si="24"/>
-        <v>-11194351</v>
+        <v>328876</v>
       </c>
       <c r="CI60" s="30">
         <f t="shared" si="25"/>
-        <v>-1</v>
+        <v>2.937874647668275E-2</v>
       </c>
       <c r="CK60" s="4" t="s">
         <v>0</v>
@@ -16135,15 +16370,15 @@
       <c r="CN60" s="2"/>
       <c r="CO60" s="6">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1721</v>
       </c>
       <c r="CP60" s="5">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="CQ60" s="30" t="e">
+        <v>-11523227</v>
+      </c>
+      <c r="CQ60" s="30">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="CS60" s="4" t="s">
         <v>0</v>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D410CDE-1F29-AA43-B257-751CAEED2528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5F87D1-1951-2443-BDB2-8DC0632DD5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15640" yWindow="3220" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1947,10 +1947,13 @@
       <c r="CD6" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="CE6" s="15">
+        <v>6</v>
+      </c>
       <c r="CF6" s="33"/>
       <c r="CG6" s="10">
         <f t="shared" si="23"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="CH6" s="12">
         <f t="shared" si="24"/>
@@ -1967,7 +1970,7 @@
       <c r="CN6" s="33"/>
       <c r="CO6" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="CP6" s="12">
         <f t="shared" si="27"/>
@@ -4881,11 +4884,13 @@
       <c r="CD17" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="CE17" s="15"/>
+      <c r="CE17" s="15">
+        <v>9</v>
+      </c>
       <c r="CF17" s="33"/>
       <c r="CG17" s="10">
         <f t="shared" si="23"/>
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="CH17" s="12">
         <f t="shared" si="24"/>
@@ -4903,7 +4908,7 @@
       <c r="CN17" s="33"/>
       <c r="CO17" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="CP17" s="12">
         <f t="shared" si="27"/>
@@ -7818,11 +7823,13 @@
       <c r="CD28" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="CE28" s="15"/>
+      <c r="CE28" s="15">
+        <v>1</v>
+      </c>
       <c r="CF28" s="33"/>
       <c r="CG28" s="10">
         <f t="shared" si="23"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="CH28" s="12">
         <f t="shared" si="24"/>
@@ -7840,7 +7847,7 @@
       <c r="CN28" s="33"/>
       <c r="CO28" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP28" s="12">
         <f t="shared" si="27"/>
@@ -10755,11 +10762,13 @@
       <c r="CD39" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="CE39" s="15"/>
+      <c r="CE39" s="15">
+        <v>1</v>
+      </c>
       <c r="CF39" s="33"/>
       <c r="CG39" s="10">
         <f t="shared" si="23"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CH39" s="12">
         <f t="shared" si="24"/>
@@ -10777,7 +10786,7 @@
       <c r="CN39" s="33"/>
       <c r="CO39" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP39" s="12">
         <f t="shared" si="27"/>
@@ -13662,11 +13671,13 @@
       <c r="CD50" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="CE50" s="15"/>
+      <c r="CE50" s="15">
+        <v>2</v>
+      </c>
       <c r="CF50" s="33"/>
       <c r="CG50" s="10">
         <f t="shared" si="23"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CH50" s="12">
         <f t="shared" si="24"/>
@@ -13684,7 +13695,7 @@
       <c r="CN50" s="33"/>
       <c r="CO50" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CP50" s="12">
         <f t="shared" si="27"/>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5F87D1-1951-2443-BDB2-8DC0632DD5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A32A97E-C30C-434A-9581-1ECAD3965AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15640" yWindow="3220" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="2880" yWindow="3580" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q4" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="52">
   <si>
     <t>總計</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>09/06-09/12</t>
+  </si>
+  <si>
+    <t>26Q4W12</t>
+  </si>
+  <si>
+    <t>09/13-09/19</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1098,9 @@
       </c>
       <c r="CD1" s="26"/>
       <c r="CF1" s="25"/>
-      <c r="CK1" s="26"/>
+      <c r="CK1" s="26" t="s">
+        <v>50</v>
+      </c>
       <c r="CL1" s="26"/>
       <c r="CN1" s="25"/>
       <c r="CS1" s="26"/>
@@ -1171,6 +1179,9 @@
       <c r="CG2" s="21"/>
       <c r="CH2" s="21"/>
       <c r="CI2" s="21"/>
+      <c r="CK2" s="20" t="s">
+        <v>51</v>
+      </c>
       <c r="CL2" s="21"/>
       <c r="CN2" s="21"/>
       <c r="CO2" s="21"/>
@@ -1422,16 +1433,16 @@
         <v>13</v>
       </c>
       <c r="CK4" s="19" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="CL4" s="19" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="CM4" s="18" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="CN4" s="17" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="CO4" s="16" t="s">
         <v>13</v>
@@ -1713,13 +1724,15 @@
         <v>75</v>
       </c>
       <c r="CL5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CM5" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CM5" s="15">
+        <v>16861</v>
+      </c>
       <c r="CN5" s="33"/>
       <c r="CO5" s="10">
         <f t="shared" ref="CO5:CO60" si="26">CM5-CE5</f>
-        <v>-7657</v>
+        <v>9204</v>
       </c>
       <c r="CP5" s="12">
         <f t="shared" ref="CP5:CP60" si="27">CN5-CF5</f>
@@ -1740,7 +1753,7 @@
       <c r="CV5" s="33"/>
       <c r="CW5" s="10">
         <f t="shared" ref="CW5:CW60" si="29">CU5-CM5</f>
-        <v>0</v>
+        <v>-16861</v>
       </c>
       <c r="CX5" s="12">
         <f t="shared" ref="CX5:CX60" si="30">CV5-CN5</f>
@@ -1965,7 +1978,7 @@
       </c>
       <c r="CK6" s="14"/>
       <c r="CL6" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CN6" s="33"/>
       <c r="CO6" s="10">
@@ -2235,18 +2248,23 @@
       <c r="CL7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN7" s="12"/>
+      <c r="CM7" s="10">
+        <v>274</v>
+      </c>
+      <c r="CN7" s="12">
+        <v>282453</v>
+      </c>
       <c r="CO7" s="10">
         <f t="shared" si="26"/>
-        <v>-142</v>
+        <v>132</v>
       </c>
       <c r="CP7" s="12">
         <f t="shared" si="27"/>
-        <v>-157770</v>
+        <v>124683</v>
       </c>
       <c r="CQ7" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.79028332382582245</v>
       </c>
       <c r="CS7" s="14"/>
       <c r="CT7" s="13" t="s">
@@ -2255,15 +2273,15 @@
       <c r="CV7" s="12"/>
       <c r="CW7" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-274</v>
       </c>
       <c r="CX7" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY7" s="11" t="e">
+        <v>-282453</v>
+      </c>
+      <c r="CY7" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -2503,18 +2521,23 @@
       <c r="CL8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN8" s="12"/>
+      <c r="CM8" s="10">
+        <v>345</v>
+      </c>
+      <c r="CN8" s="12">
+        <v>386619</v>
+      </c>
       <c r="CO8" s="10">
         <f t="shared" si="26"/>
-        <v>-229</v>
+        <v>116</v>
       </c>
       <c r="CP8" s="12">
         <f t="shared" si="27"/>
-        <v>-258686</v>
+        <v>127933</v>
       </c>
       <c r="CQ8" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.49454937646413027</v>
       </c>
       <c r="CS8" s="14"/>
       <c r="CT8" s="13" t="s">
@@ -2523,15 +2546,15 @@
       <c r="CV8" s="12"/>
       <c r="CW8" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-345</v>
       </c>
       <c r="CX8" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY8" s="11" t="e">
+        <v>-386619</v>
+      </c>
+      <c r="CY8" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -2771,18 +2794,23 @@
       <c r="CL9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN9" s="12"/>
+      <c r="CM9" s="10">
+        <v>84</v>
+      </c>
+      <c r="CN9" s="12">
+        <v>459390</v>
+      </c>
       <c r="CO9" s="10">
         <f t="shared" si="26"/>
-        <v>-37</v>
+        <v>47</v>
       </c>
       <c r="CP9" s="12">
         <f t="shared" si="27"/>
-        <v>-265076</v>
+        <v>194314</v>
       </c>
       <c r="CQ9" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.73305014410961389</v>
       </c>
       <c r="CS9" s="14"/>
       <c r="CT9" s="13" t="s">
@@ -2791,15 +2819,15 @@
       <c r="CV9" s="12"/>
       <c r="CW9" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-84</v>
       </c>
       <c r="CX9" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY9" s="11" t="e">
+        <v>-459390</v>
+      </c>
+      <c r="CY9" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3039,14 +3067,19 @@
       <c r="CL10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CN10" s="12"/>
+      <c r="CM10" s="10">
+        <v>68</v>
+      </c>
+      <c r="CN10" s="12">
+        <v>1208762</v>
+      </c>
       <c r="CO10" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="CP10" s="12">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1208762</v>
       </c>
       <c r="CQ10" s="11" t="e">
         <f t="shared" si="28"/>
@@ -3059,15 +3092,15 @@
       <c r="CV10" s="12"/>
       <c r="CW10" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="CX10" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY10" s="11" t="e">
+        <v>-1208762</v>
+      </c>
+      <c r="CY10" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3307,18 +3340,23 @@
       <c r="CL11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN11" s="12"/>
+      <c r="CM11" s="10">
+        <v>18</v>
+      </c>
+      <c r="CN11" s="12">
+        <v>112120</v>
+      </c>
       <c r="CO11" s="10">
         <f t="shared" si="26"/>
-        <v>-5</v>
+        <v>13</v>
       </c>
       <c r="CP11" s="12">
         <f t="shared" si="27"/>
-        <v>-40850</v>
+        <v>71270</v>
       </c>
       <c r="CQ11" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>1.7446756425948593</v>
       </c>
       <c r="CS11" s="14"/>
       <c r="CT11" s="13" t="s">
@@ -3327,15 +3365,15 @@
       <c r="CV11" s="12"/>
       <c r="CW11" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="CX11" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY11" s="11" t="e">
+        <v>-112120</v>
+      </c>
+      <c r="CY11" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3575,18 +3613,23 @@
       <c r="CL12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN12" s="12"/>
+      <c r="CM12" s="10">
+        <v>24</v>
+      </c>
+      <c r="CN12" s="12">
+        <v>1108019</v>
+      </c>
       <c r="CO12" s="10">
         <f t="shared" si="26"/>
-        <v>-22</v>
+        <v>2</v>
       </c>
       <c r="CP12" s="12">
         <f t="shared" si="27"/>
-        <v>-972138</v>
+        <v>135881</v>
       </c>
       <c r="CQ12" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.13977542283091496</v>
       </c>
       <c r="CS12" s="14"/>
       <c r="CT12" s="13" t="s">
@@ -3595,15 +3638,15 @@
       <c r="CV12" s="12"/>
       <c r="CW12" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="CX12" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY12" s="11" t="e">
+        <v>-1108019</v>
+      </c>
+      <c r="CY12" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3843,18 +3886,23 @@
       <c r="CL13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN13" s="12"/>
+      <c r="CM13" s="10">
+        <v>48</v>
+      </c>
+      <c r="CN13" s="12">
+        <v>1098667</v>
+      </c>
       <c r="CO13" s="10">
         <f t="shared" si="26"/>
-        <v>-46</v>
+        <v>2</v>
       </c>
       <c r="CP13" s="12">
         <f t="shared" si="27"/>
-        <v>-988381</v>
+        <v>110286</v>
       </c>
       <c r="CQ13" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.11158247679791497</v>
       </c>
       <c r="CS13" s="14"/>
       <c r="CT13" s="13" t="s">
@@ -3863,15 +3911,15 @@
       <c r="CV13" s="12"/>
       <c r="CW13" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="CX13" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY13" s="11" t="e">
+        <v>-1098667</v>
+      </c>
+      <c r="CY13" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -4111,18 +4159,23 @@
       <c r="CL14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN14" s="12"/>
+      <c r="CM14" s="10">
+        <v>439</v>
+      </c>
+      <c r="CN14" s="12">
+        <v>20889619</v>
+      </c>
       <c r="CO14" s="10">
         <f t="shared" si="26"/>
-        <v>-26</v>
+        <v>413</v>
       </c>
       <c r="CP14" s="12">
         <f t="shared" si="27"/>
-        <v>-929905</v>
+        <v>19959714</v>
       </c>
       <c r="CQ14" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>21.464250649259871</v>
       </c>
       <c r="CS14" s="14"/>
       <c r="CT14" s="13" t="s">
@@ -4131,15 +4184,15 @@
       <c r="CV14" s="12"/>
       <c r="CW14" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-439</v>
       </c>
       <c r="CX14" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY14" s="11" t="e">
+        <v>-20889619</v>
+      </c>
+      <c r="CY14" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -4377,22 +4430,26 @@
         <v>-0.30915216965211945</v>
       </c>
       <c r="CK15" s="9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="CL15" s="9"/>
-      <c r="CM15" s="8"/>
-      <c r="CN15" s="7"/>
+      <c r="CM15" s="8">
+        <v>1300</v>
+      </c>
+      <c r="CN15" s="7">
+        <v>25545649</v>
+      </c>
       <c r="CO15" s="27">
         <f t="shared" si="26"/>
-        <v>-507</v>
+        <v>793</v>
       </c>
       <c r="CP15" s="28">
         <f t="shared" si="27"/>
-        <v>-3612806</v>
+        <v>21932843</v>
       </c>
       <c r="CQ15" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>6.0708609872769257</v>
       </c>
       <c r="CS15" s="9" t="s">
         <v>18</v>
@@ -4402,15 +4459,15 @@
       <c r="CV15" s="7"/>
       <c r="CW15" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="CX15" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY15" s="29" t="e">
+        <v>-25545649</v>
+      </c>
+      <c r="CY15" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -4651,13 +4708,15 @@
         <v>76</v>
       </c>
       <c r="CL16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CM16" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CM16" s="15">
+        <v>12269</v>
+      </c>
       <c r="CN16" s="33"/>
       <c r="CO16" s="10">
         <f t="shared" si="26"/>
-        <v>-6869</v>
+        <v>5400</v>
       </c>
       <c r="CP16" s="12">
         <f t="shared" si="27"/>
@@ -4677,7 +4736,7 @@
       <c r="CV16" s="33"/>
       <c r="CW16" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-12269</v>
       </c>
       <c r="CX16" s="12">
         <f t="shared" si="30"/>
@@ -4902,7 +4961,7 @@
       </c>
       <c r="CK17" s="14"/>
       <c r="CL17" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CM17" s="15"/>
       <c r="CN17" s="33"/>
@@ -5174,18 +5233,23 @@
       <c r="CL18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN18" s="12"/>
+      <c r="CM18" s="10">
+        <v>210</v>
+      </c>
+      <c r="CN18" s="12">
+        <v>238942</v>
+      </c>
       <c r="CO18" s="10">
         <f t="shared" si="26"/>
-        <v>-139</v>
+        <v>71</v>
       </c>
       <c r="CP18" s="12">
         <f t="shared" si="27"/>
-        <v>-156901</v>
+        <v>82041</v>
       </c>
       <c r="CQ18" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.52288385669944737</v>
       </c>
       <c r="CS18" s="14"/>
       <c r="CT18" s="13" t="s">
@@ -5194,15 +5258,15 @@
       <c r="CV18" s="12"/>
       <c r="CW18" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-210</v>
       </c>
       <c r="CX18" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY18" s="11" t="e">
+        <v>-238942</v>
+      </c>
+      <c r="CY18" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -5442,18 +5506,23 @@
       <c r="CL19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN19" s="12"/>
+      <c r="CM19" s="10">
+        <v>269</v>
+      </c>
+      <c r="CN19" s="12">
+        <v>316922</v>
+      </c>
       <c r="CO19" s="10">
         <f t="shared" si="26"/>
-        <v>-245</v>
+        <v>24</v>
       </c>
       <c r="CP19" s="12">
         <f t="shared" si="27"/>
-        <v>-238287</v>
+        <v>78635</v>
       </c>
       <c r="CQ19" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.33000121701981222</v>
       </c>
       <c r="CS19" s="14"/>
       <c r="CT19" s="13" t="s">
@@ -5462,15 +5531,15 @@
       <c r="CV19" s="12"/>
       <c r="CW19" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-269</v>
       </c>
       <c r="CX19" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY19" s="11" t="e">
+        <v>-316922</v>
+      </c>
+      <c r="CY19" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -5710,18 +5779,23 @@
       <c r="CL20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN20" s="12"/>
+      <c r="CM20" s="10">
+        <v>83</v>
+      </c>
+      <c r="CN20" s="12">
+        <v>435686</v>
+      </c>
       <c r="CO20" s="10">
         <f t="shared" si="26"/>
-        <v>-33</v>
+        <v>50</v>
       </c>
       <c r="CP20" s="12">
         <f t="shared" si="27"/>
-        <v>-232638</v>
+        <v>203048</v>
       </c>
       <c r="CQ20" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.87280667818671065</v>
       </c>
       <c r="CS20" s="14"/>
       <c r="CT20" s="13" t="s">
@@ -5730,15 +5804,15 @@
       <c r="CV20" s="12"/>
       <c r="CW20" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-83</v>
       </c>
       <c r="CX20" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY20" s="11" t="e">
+        <v>-435686</v>
+      </c>
+      <c r="CY20" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -5978,18 +6052,23 @@
       <c r="CL21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CN21" s="12"/>
+      <c r="CM21" s="10">
+        <v>33</v>
+      </c>
+      <c r="CN21" s="12">
+        <v>553524</v>
+      </c>
       <c r="CO21" s="10">
         <f t="shared" si="26"/>
-        <v>-1</v>
+        <v>32</v>
       </c>
       <c r="CP21" s="12">
         <f t="shared" si="27"/>
-        <v>-13238</v>
+        <v>540286</v>
       </c>
       <c r="CQ21" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>40.81326484363197</v>
       </c>
       <c r="CS21" s="14"/>
       <c r="CT21" s="13" t="s">
@@ -5998,15 +6077,15 @@
       <c r="CV21" s="12"/>
       <c r="CW21" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="CX21" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY21" s="11" t="e">
+        <v>-553524</v>
+      </c>
+      <c r="CY21" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6246,18 +6325,23 @@
       <c r="CL22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN22" s="12"/>
+      <c r="CM22" s="10">
+        <v>19</v>
+      </c>
+      <c r="CN22" s="12">
+        <v>118310</v>
+      </c>
       <c r="CO22" s="10">
         <f t="shared" si="26"/>
-        <v>-18</v>
+        <v>1</v>
       </c>
       <c r="CP22" s="12">
         <f t="shared" si="27"/>
-        <v>-90450</v>
+        <v>27860</v>
       </c>
       <c r="CQ22" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.3080154781647319</v>
       </c>
       <c r="CS22" s="14"/>
       <c r="CT22" s="13" t="s">
@@ -6266,15 +6350,15 @@
       <c r="CV22" s="12"/>
       <c r="CW22" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="CX22" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY22" s="11" t="e">
+        <v>-118310</v>
+      </c>
+      <c r="CY22" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6514,18 +6598,23 @@
       <c r="CL23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN23" s="12"/>
+      <c r="CM23" s="10">
+        <v>25</v>
+      </c>
+      <c r="CN23" s="12">
+        <v>952124</v>
+      </c>
       <c r="CO23" s="10">
         <f t="shared" si="26"/>
-        <v>-24</v>
+        <v>1</v>
       </c>
       <c r="CP23" s="12">
         <f t="shared" si="27"/>
-        <v>-838090</v>
+        <v>114034</v>
       </c>
       <c r="CQ23" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.13606414585545706</v>
       </c>
       <c r="CS23" s="14"/>
       <c r="CT23" s="13" t="s">
@@ -6534,15 +6623,15 @@
       <c r="CV23" s="12"/>
       <c r="CW23" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="CX23" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY23" s="11" t="e">
+        <v>-952124</v>
+      </c>
+      <c r="CY23" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6782,18 +6871,23 @@
       <c r="CL24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN24" s="12"/>
+      <c r="CM24" s="10">
+        <v>38</v>
+      </c>
+      <c r="CN24" s="12">
+        <v>884381</v>
+      </c>
       <c r="CO24" s="10">
         <f t="shared" si="26"/>
-        <v>-61</v>
+        <v>-23</v>
       </c>
       <c r="CP24" s="12">
         <f t="shared" si="27"/>
-        <v>-1395048</v>
+        <v>-510667</v>
       </c>
       <c r="CQ24" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.36605693854261645</v>
       </c>
       <c r="CS24" s="14"/>
       <c r="CT24" s="13" t="s">
@@ -6802,15 +6896,15 @@
       <c r="CV24" s="12"/>
       <c r="CW24" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="CX24" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY24" s="11" t="e">
+        <v>-884381</v>
+      </c>
+      <c r="CY24" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -7050,18 +7144,23 @@
       <c r="CL25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN25" s="12"/>
+      <c r="CM25" s="10">
+        <v>259</v>
+      </c>
+      <c r="CN25" s="12">
+        <v>11919143</v>
+      </c>
       <c r="CO25" s="10">
         <f t="shared" si="26"/>
-        <v>-54</v>
+        <v>205</v>
       </c>
       <c r="CP25" s="12">
         <f t="shared" si="27"/>
-        <v>-1783098</v>
+        <v>10136045</v>
       </c>
       <c r="CQ25" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>5.6845136947043855</v>
       </c>
       <c r="CS25" s="14"/>
       <c r="CT25" s="13" t="s">
@@ -7070,15 +7169,15 @@
       <c r="CV25" s="12"/>
       <c r="CW25" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-259</v>
       </c>
       <c r="CX25" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY25" s="11" t="e">
+        <v>-11919143</v>
+      </c>
+      <c r="CY25" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -7319,19 +7418,23 @@
         <v>12</v>
       </c>
       <c r="CL26" s="9"/>
-      <c r="CM26" s="8"/>
-      <c r="CN26" s="7"/>
+      <c r="CM26" s="8">
+        <v>936</v>
+      </c>
+      <c r="CN26" s="7">
+        <v>15419032</v>
+      </c>
       <c r="CO26" s="27">
         <f t="shared" si="26"/>
-        <v>-575</v>
+        <v>361</v>
       </c>
       <c r="CP26" s="28">
         <f t="shared" si="27"/>
-        <v>-4747750</v>
+        <v>10671282</v>
       </c>
       <c r="CQ26" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>2.2476503606971723</v>
       </c>
       <c r="CS26" s="9" t="s">
         <v>12</v>
@@ -7341,15 +7444,15 @@
       <c r="CV26" s="7"/>
       <c r="CW26" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-936</v>
       </c>
       <c r="CX26" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY26" s="29" t="e">
+        <v>-15419032</v>
+      </c>
+      <c r="CY26" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -7590,13 +7693,15 @@
         <v>77</v>
       </c>
       <c r="CL27" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CM27" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CM27" s="15">
+        <v>7954</v>
+      </c>
       <c r="CN27" s="33"/>
       <c r="CO27" s="10">
         <f t="shared" si="26"/>
-        <v>-4471</v>
+        <v>3483</v>
       </c>
       <c r="CP27" s="12">
         <f t="shared" si="27"/>
@@ -7616,7 +7721,7 @@
       <c r="CV27" s="33"/>
       <c r="CW27" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-7954</v>
       </c>
       <c r="CX27" s="12">
         <f t="shared" si="30"/>
@@ -7841,7 +7946,7 @@
       </c>
       <c r="CK28" s="14"/>
       <c r="CL28" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CM28" s="15"/>
       <c r="CN28" s="33"/>
@@ -8113,18 +8218,23 @@
       <c r="CL29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN29" s="12"/>
+      <c r="CM29" s="10">
+        <v>132</v>
+      </c>
+      <c r="CN29" s="12">
+        <v>122216</v>
+      </c>
       <c r="CO29" s="10">
         <f t="shared" si="26"/>
-        <v>-56</v>
+        <v>76</v>
       </c>
       <c r="CP29" s="12">
         <f t="shared" si="27"/>
-        <v>-55918</v>
+        <v>66298</v>
       </c>
       <c r="CQ29" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>1.1856289566865768</v>
       </c>
       <c r="CS29" s="14"/>
       <c r="CT29" s="13" t="s">
@@ -8133,15 +8243,15 @@
       <c r="CV29" s="12"/>
       <c r="CW29" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-132</v>
       </c>
       <c r="CX29" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY29" s="11" t="e">
+        <v>-122216</v>
+      </c>
+      <c r="CY29" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -8381,18 +8491,23 @@
       <c r="CL30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN30" s="12"/>
+      <c r="CM30" s="10">
+        <v>75</v>
+      </c>
+      <c r="CN30" s="12">
+        <v>72145</v>
+      </c>
       <c r="CO30" s="10">
         <f t="shared" si="26"/>
-        <v>-77</v>
+        <v>-2</v>
       </c>
       <c r="CP30" s="12">
         <f t="shared" si="27"/>
-        <v>-71239</v>
+        <v>906</v>
       </c>
       <c r="CQ30" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>1.2717752916239701E-2</v>
       </c>
       <c r="CS30" s="14"/>
       <c r="CT30" s="13" t="s">
@@ -8401,15 +8516,15 @@
       <c r="CV30" s="12"/>
       <c r="CW30" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="CX30" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY30" s="11" t="e">
+        <v>-72145</v>
+      </c>
+      <c r="CY30" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="31" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -8649,18 +8764,23 @@
       <c r="CL31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN31" s="12"/>
+      <c r="CM31" s="10">
+        <v>13</v>
+      </c>
+      <c r="CN31" s="12">
+        <v>87210</v>
+      </c>
       <c r="CO31" s="10">
         <f t="shared" si="26"/>
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="CP31" s="12">
         <f t="shared" si="27"/>
-        <v>-84733</v>
+        <v>2477</v>
       </c>
       <c r="CQ31" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>2.923300249017502E-2</v>
       </c>
       <c r="CS31" s="14"/>
       <c r="CT31" s="13" t="s">
@@ -8669,15 +8789,15 @@
       <c r="CV31" s="12"/>
       <c r="CW31" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="CX31" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY31" s="11" t="e">
+        <v>-87210</v>
+      </c>
+      <c r="CY31" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -8917,18 +9037,23 @@
       <c r="CL32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CN32" s="12"/>
+      <c r="CM32" s="10">
+        <v>21</v>
+      </c>
+      <c r="CN32" s="12">
+        <v>345619</v>
+      </c>
       <c r="CO32" s="10">
         <f t="shared" si="26"/>
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CP32" s="12">
         <f t="shared" si="27"/>
-        <v>-7524</v>
+        <v>338095</v>
       </c>
       <c r="CQ32" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>44.935539606592236</v>
       </c>
       <c r="CS32" s="14"/>
       <c r="CT32" s="13" t="s">
@@ -8937,15 +9062,15 @@
       <c r="CV32" s="12"/>
       <c r="CW32" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="CX32" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY32" s="11" t="e">
+        <v>-345619</v>
+      </c>
+      <c r="CY32" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9185,18 +9310,23 @@
       <c r="CL33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN33" s="12"/>
+      <c r="CM33" s="10">
+        <v>6</v>
+      </c>
+      <c r="CN33" s="12">
+        <v>34040</v>
+      </c>
       <c r="CO33" s="10">
         <f t="shared" si="26"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="CP33" s="12">
         <f t="shared" si="27"/>
-        <v>-20650</v>
+        <v>13390</v>
       </c>
       <c r="CQ33" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.64842615012106541</v>
       </c>
       <c r="CS33" s="14"/>
       <c r="CT33" s="13" t="s">
@@ -9205,15 +9335,15 @@
       <c r="CV33" s="12"/>
       <c r="CW33" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="CX33" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY33" s="11" t="e">
+        <v>-34040</v>
+      </c>
+      <c r="CY33" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9453,18 +9583,23 @@
       <c r="CL34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN34" s="12"/>
+      <c r="CM34" s="10">
+        <v>3</v>
+      </c>
+      <c r="CN34" s="12">
+        <v>114952</v>
+      </c>
       <c r="CO34" s="10">
         <f t="shared" si="26"/>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="CP34" s="12">
         <f t="shared" si="27"/>
-        <v>-116713</v>
+        <v>-1761</v>
       </c>
       <c r="CQ34" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-1.5088293506293215E-2</v>
       </c>
       <c r="CS34" s="14"/>
       <c r="CT34" s="13" t="s">
@@ -9473,15 +9608,15 @@
       <c r="CV34" s="12"/>
       <c r="CW34" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="CX34" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY34" s="11" t="e">
+        <v>-114952</v>
+      </c>
+      <c r="CY34" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9721,18 +9856,23 @@
       <c r="CL35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN35" s="12"/>
+      <c r="CM35" s="10">
+        <v>14</v>
+      </c>
+      <c r="CN35" s="12">
+        <v>291238</v>
+      </c>
       <c r="CO35" s="10">
         <f t="shared" si="26"/>
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="CP35" s="12">
         <f t="shared" si="27"/>
-        <v>-247714</v>
+        <v>43524</v>
       </c>
       <c r="CQ35" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.17570262480118201</v>
       </c>
       <c r="CS35" s="14"/>
       <c r="CT35" s="13" t="s">
@@ -9741,15 +9881,15 @@
       <c r="CV35" s="12"/>
       <c r="CW35" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="CX35" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY35" s="11" t="e">
+        <v>-291238</v>
+      </c>
+      <c r="CY35" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9989,18 +10129,23 @@
       <c r="CL36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN36" s="12"/>
+      <c r="CM36" s="10">
+        <v>108</v>
+      </c>
+      <c r="CN36" s="12">
+        <v>5045905</v>
+      </c>
       <c r="CO36" s="10">
         <f t="shared" si="26"/>
-        <v>-4</v>
+        <v>104</v>
       </c>
       <c r="CP36" s="12">
         <f t="shared" si="27"/>
-        <v>-142476</v>
+        <v>4903429</v>
       </c>
       <c r="CQ36" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>34.415824419551363</v>
       </c>
       <c r="CS36" s="14"/>
       <c r="CT36" s="13" t="s">
@@ -10009,15 +10154,15 @@
       <c r="CV36" s="12"/>
       <c r="CW36" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-108</v>
       </c>
       <c r="CX36" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY36" s="11" t="e">
+        <v>-5045905</v>
+      </c>
+      <c r="CY36" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -10258,19 +10403,23 @@
         <v>11</v>
       </c>
       <c r="CL37" s="9"/>
-      <c r="CM37" s="8"/>
-      <c r="CN37" s="7"/>
+      <c r="CM37" s="8">
+        <v>372</v>
+      </c>
+      <c r="CN37" s="7">
+        <v>6113325</v>
+      </c>
       <c r="CO37" s="27">
         <f t="shared" si="26"/>
-        <v>-169</v>
+        <v>203</v>
       </c>
       <c r="CP37" s="28">
         <f t="shared" si="27"/>
-        <v>-746967</v>
+        <v>5366358</v>
       </c>
       <c r="CQ37" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>7.1841968922321868</v>
       </c>
       <c r="CS37" s="9" t="s">
         <v>11</v>
@@ -10280,15 +10429,15 @@
       <c r="CV37" s="7"/>
       <c r="CW37" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-372</v>
       </c>
       <c r="CX37" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY37" s="29" t="e">
+        <v>-6113325</v>
+      </c>
+      <c r="CY37" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -10529,13 +10678,15 @@
         <v>81</v>
       </c>
       <c r="CL38" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CM38" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CM38" s="15">
+        <v>5160</v>
+      </c>
       <c r="CN38" s="33"/>
       <c r="CO38" s="10">
         <f t="shared" si="26"/>
-        <v>-2314</v>
+        <v>2846</v>
       </c>
       <c r="CP38" s="12">
         <f t="shared" si="27"/>
@@ -10555,7 +10706,7 @@
       <c r="CV38" s="33"/>
       <c r="CW38" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-5160</v>
       </c>
       <c r="CX38" s="12">
         <f t="shared" si="30"/>
@@ -10780,7 +10931,7 @@
       </c>
       <c r="CK39" s="14"/>
       <c r="CL39" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CM39" s="15"/>
       <c r="CN39" s="33"/>
@@ -11052,18 +11203,23 @@
       <c r="CL40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN40" s="12"/>
+      <c r="CM40" s="10">
+        <v>216</v>
+      </c>
+      <c r="CN40" s="12">
+        <v>223403</v>
+      </c>
       <c r="CO40" s="10">
         <f t="shared" si="26"/>
-        <v>-105</v>
+        <v>111</v>
       </c>
       <c r="CP40" s="12">
         <f t="shared" si="27"/>
-        <v>-99201</v>
+        <v>124202</v>
       </c>
       <c r="CQ40" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>1.2520236691162387</v>
       </c>
       <c r="CS40" s="14"/>
       <c r="CT40" s="13" t="s">
@@ -11072,15 +11228,15 @@
       <c r="CV40" s="12"/>
       <c r="CW40" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-216</v>
       </c>
       <c r="CX40" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY40" s="11" t="e">
+        <v>-223403</v>
+      </c>
+      <c r="CY40" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -11320,18 +11476,23 @@
       <c r="CL41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN41" s="12"/>
+      <c r="CM41" s="10">
+        <v>108</v>
+      </c>
+      <c r="CN41" s="12">
+        <v>107782</v>
+      </c>
       <c r="CO41" s="10">
         <f t="shared" si="26"/>
-        <v>-103</v>
+        <v>5</v>
       </c>
       <c r="CP41" s="12">
         <f t="shared" si="27"/>
-        <v>-116981</v>
+        <v>-9199</v>
       </c>
       <c r="CQ41" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-7.8636701686598684E-2</v>
       </c>
       <c r="CS41" s="14"/>
       <c r="CT41" s="13" t="s">
@@ -11340,15 +11501,15 @@
       <c r="CV41" s="12"/>
       <c r="CW41" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-108</v>
       </c>
       <c r="CX41" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY41" s="11" t="e">
+        <v>-107782</v>
+      </c>
+      <c r="CY41" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -11588,18 +11749,23 @@
       <c r="CL42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN42" s="12"/>
+      <c r="CM42" s="10">
+        <v>11</v>
+      </c>
+      <c r="CN42" s="12">
+        <v>70086</v>
+      </c>
       <c r="CO42" s="10">
         <f t="shared" si="26"/>
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="CP42" s="12">
         <f t="shared" si="27"/>
-        <v>-75905</v>
+        <v>-5819</v>
       </c>
       <c r="CQ42" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-7.6661616494302087E-2</v>
       </c>
       <c r="CS42" s="14"/>
       <c r="CT42" s="13" t="s">
@@ -11608,15 +11774,15 @@
       <c r="CV42" s="12"/>
       <c r="CW42" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="CX42" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY42" s="11" t="e">
+        <v>-70086</v>
+      </c>
+      <c r="CY42" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -11856,18 +12022,23 @@
       <c r="CL43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CN43" s="12"/>
+      <c r="CM43" s="10">
+        <v>15</v>
+      </c>
+      <c r="CN43" s="12">
+        <v>273333</v>
+      </c>
       <c r="CO43" s="10">
         <f t="shared" si="26"/>
-        <v>-2</v>
+        <v>13</v>
       </c>
       <c r="CP43" s="12">
         <f t="shared" si="27"/>
-        <v>-15048</v>
+        <v>258285</v>
       </c>
       <c r="CQ43" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>17.164074960127593</v>
       </c>
       <c r="CS43" s="14"/>
       <c r="CT43" s="13" t="s">
@@ -11876,15 +12047,15 @@
       <c r="CV43" s="12"/>
       <c r="CW43" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="CX43" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY43" s="11" t="e">
+        <v>-273333</v>
+      </c>
+      <c r="CY43" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12124,18 +12295,23 @@
       <c r="CL44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN44" s="12"/>
+      <c r="CM44" s="10">
+        <v>6</v>
+      </c>
+      <c r="CN44" s="12">
+        <v>38940</v>
+      </c>
       <c r="CO44" s="10">
         <f t="shared" si="26"/>
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CP44" s="12">
         <f t="shared" si="27"/>
-        <v>-6990</v>
+        <v>31950</v>
       </c>
       <c r="CQ44" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>4.570815450643777</v>
       </c>
       <c r="CS44" s="14"/>
       <c r="CT44" s="13" t="s">
@@ -12144,15 +12320,15 @@
       <c r="CV44" s="12"/>
       <c r="CW44" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="CX44" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY44" s="11" t="e">
+        <v>-38940</v>
+      </c>
+      <c r="CY44" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12392,18 +12568,23 @@
       <c r="CL45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN45" s="12"/>
+      <c r="CM45" s="10">
+        <v>10</v>
+      </c>
+      <c r="CN45" s="12">
+        <v>312388</v>
+      </c>
       <c r="CO45" s="10">
         <f t="shared" si="26"/>
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="CP45" s="12">
         <f t="shared" si="27"/>
-        <v>-112952</v>
+        <v>199436</v>
       </c>
       <c r="CQ45" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>1.7656703732558963</v>
       </c>
       <c r="CS45" s="14"/>
       <c r="CT45" s="13" t="s">
@@ -12412,15 +12593,15 @@
       <c r="CV45" s="12"/>
       <c r="CW45" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="CX45" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY45" s="11" t="e">
+        <v>-312388</v>
+      </c>
+      <c r="CY45" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12660,18 +12841,23 @@
       <c r="CL46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN46" s="12"/>
+      <c r="CM46" s="10">
+        <v>14</v>
+      </c>
+      <c r="CN46" s="12">
+        <v>310381</v>
+      </c>
       <c r="CO46" s="10">
         <f t="shared" si="26"/>
-        <v>-24</v>
+        <v>-10</v>
       </c>
       <c r="CP46" s="12">
         <f t="shared" si="27"/>
-        <v>-543524</v>
+        <v>-233143</v>
       </c>
       <c r="CQ46" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.42894701981881206</v>
       </c>
       <c r="CS46" s="14"/>
       <c r="CT46" s="13" t="s">
@@ -12680,15 +12866,15 @@
       <c r="CV46" s="12"/>
       <c r="CW46" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="CX46" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY46" s="11" t="e">
+        <v>-310381</v>
+      </c>
+      <c r="CY46" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12928,18 +13114,23 @@
       <c r="CL47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN47" s="12"/>
+      <c r="CM47" s="10">
+        <v>131</v>
+      </c>
+      <c r="CN47" s="12">
+        <v>6077048</v>
+      </c>
       <c r="CO47" s="10">
         <f t="shared" si="26"/>
-        <v>-10</v>
+        <v>121</v>
       </c>
       <c r="CP47" s="12">
         <f t="shared" si="27"/>
-        <v>-400000</v>
+        <v>5677048</v>
       </c>
       <c r="CQ47" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>14.19262</v>
       </c>
       <c r="CS47" s="14"/>
       <c r="CT47" s="13" t="s">
@@ -12948,15 +13139,15 @@
       <c r="CV47" s="12"/>
       <c r="CW47" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-131</v>
       </c>
       <c r="CX47" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY47" s="11" t="e">
+        <v>-6077048</v>
+      </c>
+      <c r="CY47" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -13197,19 +13388,23 @@
         <v>10</v>
       </c>
       <c r="CL48" s="9"/>
-      <c r="CM48" s="8"/>
-      <c r="CN48" s="7"/>
+      <c r="CM48" s="8">
+        <v>511</v>
+      </c>
+      <c r="CN48" s="7">
+        <v>7413361</v>
+      </c>
       <c r="CO48" s="27">
         <f t="shared" si="26"/>
-        <v>-259</v>
+        <v>252</v>
       </c>
       <c r="CP48" s="28">
         <f t="shared" si="27"/>
-        <v>-1370601</v>
+        <v>6042760</v>
       </c>
       <c r="CQ48" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>4.4088396258283771</v>
       </c>
       <c r="CS48" s="9" t="s">
         <v>10</v>
@@ -13219,15 +13414,15 @@
       <c r="CV48" s="7"/>
       <c r="CW48" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-511</v>
       </c>
       <c r="CX48" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY48" s="29" t="e">
+        <v>-7413361</v>
+      </c>
+      <c r="CY48" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -13438,7 +13633,7 @@
         <v>84</v>
       </c>
       <c r="CL49" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CM49" s="15"/>
       <c r="CN49" s="33"/>
@@ -13689,7 +13884,7 @@
       </c>
       <c r="CK50" s="14"/>
       <c r="CL50" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="CM50" s="15"/>
       <c r="CN50" s="33"/>
@@ -13961,18 +14156,23 @@
       <c r="CL51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CN51" s="12"/>
+      <c r="CM51" s="10">
+        <v>177</v>
+      </c>
+      <c r="CN51" s="12">
+        <v>167083</v>
+      </c>
       <c r="CO51" s="10">
         <f t="shared" si="26"/>
-        <v>-90</v>
+        <v>87</v>
       </c>
       <c r="CP51" s="12">
         <f t="shared" si="27"/>
-        <v>-89890</v>
+        <v>77193</v>
       </c>
       <c r="CQ51" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.85874958282345093</v>
       </c>
       <c r="CS51" s="14"/>
       <c r="CT51" s="13" t="s">
@@ -13981,15 +14181,15 @@
       <c r="CV51" s="12"/>
       <c r="CW51" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-177</v>
       </c>
       <c r="CX51" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY51" s="11" t="e">
+        <v>-167083</v>
+      </c>
+      <c r="CY51" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="52" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -14229,18 +14429,23 @@
       <c r="CL52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CN52" s="12"/>
+      <c r="CM52" s="10">
+        <v>69</v>
+      </c>
+      <c r="CN52" s="12">
+        <v>69724</v>
+      </c>
       <c r="CO52" s="10">
         <f t="shared" si="26"/>
-        <v>-77</v>
+        <v>-8</v>
       </c>
       <c r="CP52" s="12">
         <f t="shared" si="27"/>
-        <v>-75171</v>
+        <v>-5447</v>
       </c>
       <c r="CQ52" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-7.2461454550292001E-2</v>
       </c>
       <c r="CS52" s="14"/>
       <c r="CT52" s="13" t="s">
@@ -14249,15 +14454,15 @@
       <c r="CV52" s="12"/>
       <c r="CW52" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-69</v>
       </c>
       <c r="CX52" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY52" s="11" t="e">
+        <v>-69724</v>
+      </c>
+      <c r="CY52" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -14497,18 +14702,23 @@
       <c r="CL53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CN53" s="12"/>
+      <c r="CM53" s="10">
+        <v>16</v>
+      </c>
+      <c r="CN53" s="12">
+        <v>96800</v>
+      </c>
       <c r="CO53" s="10">
         <f t="shared" si="26"/>
-        <v>-13</v>
+        <v>3</v>
       </c>
       <c r="CP53" s="12">
         <f t="shared" si="27"/>
-        <v>-103781</v>
+        <v>-6981</v>
       </c>
       <c r="CQ53" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-6.7266648037694762E-2</v>
       </c>
       <c r="CS53" s="14"/>
       <c r="CT53" s="13" t="s">
@@ -14517,15 +14727,15 @@
       <c r="CV53" s="12"/>
       <c r="CW53" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="CX53" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY53" s="11" t="e">
+        <v>-96800</v>
+      </c>
+      <c r="CY53" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -14765,18 +14975,23 @@
       <c r="CL54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CN54" s="12"/>
+      <c r="CM54" s="10">
+        <v>16</v>
+      </c>
+      <c r="CN54" s="12">
+        <v>252762</v>
+      </c>
       <c r="CO54" s="10">
         <f t="shared" si="26"/>
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CP54" s="12">
         <f t="shared" si="27"/>
-        <v>-7524</v>
+        <v>245238</v>
       </c>
       <c r="CQ54" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>32.59409888357257</v>
       </c>
       <c r="CS54" s="14"/>
       <c r="CT54" s="13" t="s">
@@ -14785,15 +15000,15 @@
       <c r="CV54" s="12"/>
       <c r="CW54" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="CX54" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY54" s="11" t="e">
+        <v>-252762</v>
+      </c>
+      <c r="CY54" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="55" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15033,18 +15248,23 @@
       <c r="CL55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CN55" s="12"/>
+      <c r="CM55" s="10">
+        <v>8</v>
+      </c>
+      <c r="CN55" s="12">
+        <v>42320</v>
+      </c>
       <c r="CO55" s="10">
         <f t="shared" si="26"/>
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="CP55" s="12">
         <f t="shared" si="27"/>
-        <v>-9970</v>
+        <v>32350</v>
       </c>
       <c r="CQ55" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>3.2447342026078236</v>
       </c>
       <c r="CS55" s="14"/>
       <c r="CT55" s="13" t="s">
@@ -15053,15 +15273,15 @@
       <c r="CV55" s="12"/>
       <c r="CW55" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="CX55" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY55" s="11" t="e">
+        <v>-42320</v>
+      </c>
+      <c r="CY55" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15301,18 +15521,23 @@
       <c r="CL56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CN56" s="12"/>
+      <c r="CM56" s="10">
+        <v>1</v>
+      </c>
+      <c r="CN56" s="12">
+        <v>24667</v>
+      </c>
       <c r="CO56" s="10">
         <f t="shared" si="26"/>
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="CP56" s="12">
         <f t="shared" si="27"/>
-        <v>-139524</v>
+        <v>-114857</v>
       </c>
       <c r="CQ56" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-0.82320604340471892</v>
       </c>
       <c r="CS56" s="14"/>
       <c r="CT56" s="13" t="s">
@@ -15321,15 +15546,15 @@
       <c r="CV56" s="12"/>
       <c r="CW56" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CX56" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY56" s="11" t="e">
+        <v>-24667</v>
+      </c>
+      <c r="CY56" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15569,18 +15794,23 @@
       <c r="CL57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CN57" s="12"/>
+      <c r="CM57" s="10">
+        <v>12</v>
+      </c>
+      <c r="CN57" s="12">
+        <v>285048</v>
+      </c>
       <c r="CO57" s="10">
         <f t="shared" si="26"/>
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="CP57" s="12">
         <f t="shared" si="27"/>
-        <v>-218571</v>
+        <v>66477</v>
       </c>
       <c r="CQ57" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>0.30414373361516395</v>
       </c>
       <c r="CS57" s="14"/>
       <c r="CT57" s="13" t="s">
@@ -15589,15 +15819,15 @@
       <c r="CV57" s="12"/>
       <c r="CW57" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="CX57" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY57" s="11" t="e">
+        <v>-285048</v>
+      </c>
+      <c r="CY57" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="58" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15837,18 +16067,23 @@
       <c r="CL58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CN58" s="12"/>
+      <c r="CM58" s="10">
+        <v>129</v>
+      </c>
+      <c r="CN58" s="12">
+        <v>5971261</v>
+      </c>
       <c r="CO58" s="10">
         <f t="shared" si="26"/>
-        <v>-12</v>
+        <v>117</v>
       </c>
       <c r="CP58" s="12">
         <f t="shared" si="27"/>
-        <v>-400672</v>
+        <v>5570589</v>
       </c>
       <c r="CQ58" s="11">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>13.903115266352527</v>
       </c>
       <c r="CS58" s="14"/>
       <c r="CT58" s="13" t="s">
@@ -15857,15 +16092,15 @@
       <c r="CV58" s="12"/>
       <c r="CW58" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-129</v>
       </c>
       <c r="CX58" s="12">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY58" s="11" t="e">
+        <v>-5971261</v>
+      </c>
+      <c r="CY58" s="11">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -16106,19 +16341,23 @@
         <v>1</v>
       </c>
       <c r="CL59" s="9"/>
-      <c r="CM59" s="8"/>
-      <c r="CN59" s="7"/>
+      <c r="CM59" s="8">
+        <v>428</v>
+      </c>
+      <c r="CN59" s="7">
+        <v>6909665</v>
+      </c>
       <c r="CO59" s="27">
         <f t="shared" si="26"/>
-        <v>-211</v>
+        <v>217</v>
       </c>
       <c r="CP59" s="28">
         <f t="shared" si="27"/>
-        <v>-1045103</v>
+        <v>5864562</v>
       </c>
       <c r="CQ59" s="29">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>5.6114679605742213</v>
       </c>
       <c r="CS59" s="9" t="s">
         <v>1</v>
@@ -16128,15 +16367,15 @@
       <c r="CV59" s="7"/>
       <c r="CW59" s="27">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-428</v>
       </c>
       <c r="CX59" s="28">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY59" s="29" t="e">
+        <v>-6909665</v>
+      </c>
+      <c r="CY59" s="29">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -16377,19 +16616,23 @@
         <v>0</v>
       </c>
       <c r="CL60" s="4"/>
-      <c r="CM60" s="3"/>
-      <c r="CN60" s="2"/>
+      <c r="CM60" s="3">
+        <v>3547</v>
+      </c>
+      <c r="CN60" s="2">
+        <v>61401032</v>
+      </c>
       <c r="CO60" s="6">
         <f t="shared" si="26"/>
-        <v>-1721</v>
+        <v>1826</v>
       </c>
       <c r="CP60" s="5">
         <f t="shared" si="27"/>
-        <v>-11523227</v>
+        <v>49877805</v>
       </c>
       <c r="CQ60" s="30">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>4.3284580786267597</v>
       </c>
       <c r="CS60" s="4" t="s">
         <v>0</v>
@@ -16399,15 +16642,15 @@
       <c r="CV60" s="2"/>
       <c r="CW60" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-3547</v>
       </c>
       <c r="CX60" s="5">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="CY60" s="30" t="e">
+        <v>-61401032</v>
+      </c>
+      <c r="CY60" s="30">
         <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/data/FY26Q4.xlsx
+++ b/data/FY26Q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A32A97E-C30C-434A-9581-1ECAD3965AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7553B7B1-2E62-A347-9C4D-0F03D2F0780A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="3580" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="11740" yWindow="3240" windowWidth="17760" windowHeight="15980" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q4" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="54">
   <si>
     <t>總計</t>
   </si>
@@ -245,6 +245,12 @@
   </si>
   <si>
     <t>09/13-09/19</t>
+  </si>
+  <si>
+    <t>26Q4W13</t>
+  </si>
+  <si>
+    <t>09/20-09/26</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1109,9 @@
       </c>
       <c r="CL1" s="26"/>
       <c r="CN1" s="25"/>
-      <c r="CS1" s="26"/>
+      <c r="CS1" s="26" t="s">
+        <v>52</v>
+      </c>
       <c r="CT1" s="26"/>
       <c r="CV1" s="25"/>
     </row>
@@ -1187,6 +1195,9 @@
       <c r="CO2" s="21"/>
       <c r="CP2" s="21"/>
       <c r="CQ2" s="21"/>
+      <c r="CS2" s="20" t="s">
+        <v>53</v>
+      </c>
       <c r="CT2" s="21"/>
       <c r="CV2" s="21"/>
       <c r="CW2" s="21"/>
@@ -1454,16 +1465,16 @@
         <v>13</v>
       </c>
       <c r="CS4" s="19" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="CT4" s="19" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="CU4" s="18" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="CV4" s="17" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="CW4" s="16" t="s">
         <v>13</v>
@@ -1747,13 +1758,15 @@
         <v>75</v>
       </c>
       <c r="CT5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CU5" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CU5" s="15">
+        <v>21062</v>
+      </c>
       <c r="CV5" s="33"/>
       <c r="CW5" s="10">
         <f t="shared" ref="CW5:CW60" si="29">CU5-CM5</f>
-        <v>-16861</v>
+        <v>4201</v>
       </c>
       <c r="CX5" s="12">
         <f t="shared" ref="CX5:CX60" si="30">CV5-CN5</f>
@@ -1980,10 +1993,13 @@
       <c r="CL6" s="32" t="s">
         <v>38</v>
       </c>
+      <c r="CM6" s="15">
+        <v>15</v>
+      </c>
       <c r="CN6" s="33"/>
       <c r="CO6" s="10">
         <f t="shared" si="26"/>
-        <v>-6</v>
+        <v>9</v>
       </c>
       <c r="CP6" s="12">
         <f t="shared" si="27"/>
@@ -1995,12 +2011,15 @@
       </c>
       <c r="CS6" s="14"/>
       <c r="CT6" s="32" t="s">
-        <v>20</v>
+        <v>38</v>
+      </c>
+      <c r="CU6" s="15">
+        <v>30</v>
       </c>
       <c r="CV6" s="33"/>
       <c r="CW6" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CX6" s="12">
         <f t="shared" si="30"/>
@@ -2270,18 +2289,23 @@
       <c r="CT7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV7" s="12"/>
+      <c r="CU7" s="10">
+        <v>372</v>
+      </c>
+      <c r="CV7" s="12">
+        <v>441141</v>
+      </c>
       <c r="CW7" s="10">
         <f t="shared" si="29"/>
-        <v>-274</v>
+        <v>98</v>
       </c>
       <c r="CX7" s="12">
         <f t="shared" si="30"/>
-        <v>-282453</v>
+        <v>158688</v>
       </c>
       <c r="CY7" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.56182090471689095</v>
       </c>
     </row>
     <row r="8" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -2543,18 +2567,23 @@
       <c r="CT8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV8" s="12"/>
+      <c r="CU8" s="10">
+        <v>519</v>
+      </c>
+      <c r="CV8" s="12">
+        <v>666926</v>
+      </c>
       <c r="CW8" s="10">
         <f t="shared" si="29"/>
-        <v>-345</v>
+        <v>174</v>
       </c>
       <c r="CX8" s="12">
         <f t="shared" si="30"/>
-        <v>-386619</v>
+        <v>280307</v>
       </c>
       <c r="CY8" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.72502127417431628</v>
       </c>
     </row>
     <row r="9" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -2816,18 +2845,23 @@
       <c r="CT9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV9" s="12"/>
+      <c r="CU9" s="10">
+        <v>145</v>
+      </c>
+      <c r="CV9" s="12">
+        <v>805762</v>
+      </c>
       <c r="CW9" s="10">
         <f t="shared" si="29"/>
-        <v>-84</v>
+        <v>61</v>
       </c>
       <c r="CX9" s="12">
         <f t="shared" si="30"/>
-        <v>-459390</v>
+        <v>346372</v>
       </c>
       <c r="CY9" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.75398245499466687</v>
       </c>
     </row>
     <row r="10" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3089,18 +3123,23 @@
       <c r="CT10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CV10" s="12"/>
+      <c r="CU10" s="10">
+        <v>137</v>
+      </c>
+      <c r="CV10" s="12">
+        <v>2281714</v>
+      </c>
       <c r="CW10" s="10">
         <f t="shared" si="29"/>
-        <v>-68</v>
+        <v>69</v>
       </c>
       <c r="CX10" s="12">
         <f t="shared" si="30"/>
-        <v>-1208762</v>
+        <v>1072952</v>
       </c>
       <c r="CY10" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.88764537601281313</v>
       </c>
     </row>
     <row r="11" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3362,18 +3401,23 @@
       <c r="CT11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV11" s="12"/>
+      <c r="CU11" s="10">
+        <v>27</v>
+      </c>
+      <c r="CV11" s="12">
+        <v>190730</v>
+      </c>
       <c r="CW11" s="10">
         <f t="shared" si="29"/>
-        <v>-18</v>
+        <v>9</v>
       </c>
       <c r="CX11" s="12">
         <f t="shared" si="30"/>
-        <v>-112120</v>
+        <v>78610</v>
       </c>
       <c r="CY11" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.70112379593292895</v>
       </c>
     </row>
     <row r="12" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3635,18 +3679,23 @@
       <c r="CT12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV12" s="12"/>
+      <c r="CU12" s="10">
+        <v>76</v>
+      </c>
+      <c r="CV12" s="12">
+        <v>2980019</v>
+      </c>
       <c r="CW12" s="10">
         <f t="shared" si="29"/>
-        <v>-24</v>
+        <v>52</v>
       </c>
       <c r="CX12" s="12">
         <f t="shared" si="30"/>
-        <v>-1108019</v>
+        <v>1872000</v>
       </c>
       <c r="CY12" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>1.6895017143207833</v>
       </c>
     </row>
     <row r="13" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -3908,18 +3957,23 @@
       <c r="CT13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV13" s="12"/>
+      <c r="CU13" s="10">
+        <v>101</v>
+      </c>
+      <c r="CV13" s="12">
+        <v>2393524</v>
+      </c>
       <c r="CW13" s="10">
         <f t="shared" si="29"/>
-        <v>-48</v>
+        <v>53</v>
       </c>
       <c r="CX13" s="12">
         <f t="shared" si="30"/>
-        <v>-1098667</v>
+        <v>1294857</v>
       </c>
       <c r="CY13" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>1.1785709409675542</v>
       </c>
     </row>
     <row r="14" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -4181,18 +4235,23 @@
       <c r="CT14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV14" s="12"/>
+      <c r="CU14" s="10">
+        <v>264</v>
+      </c>
+      <c r="CV14" s="12">
+        <v>13377714</v>
+      </c>
       <c r="CW14" s="10">
         <f t="shared" si="29"/>
-        <v>-439</v>
+        <v>-175</v>
       </c>
       <c r="CX14" s="12">
         <f t="shared" si="30"/>
-        <v>-20889619</v>
+        <v>-7511905</v>
       </c>
       <c r="CY14" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.35959990462248259</v>
       </c>
     </row>
     <row r="15" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -4452,22 +4511,26 @@
         <v>6.0708609872769257</v>
       </c>
       <c r="CS15" s="9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="CT15" s="9"/>
-      <c r="CU15" s="8"/>
-      <c r="CV15" s="7"/>
+      <c r="CU15" s="8">
+        <v>1641</v>
+      </c>
+      <c r="CV15" s="7">
+        <v>23137530</v>
+      </c>
       <c r="CW15" s="27">
         <f t="shared" si="29"/>
-        <v>-1300</v>
+        <v>341</v>
       </c>
       <c r="CX15" s="28">
         <f t="shared" si="30"/>
-        <v>-25545649</v>
+        <v>-2408119</v>
       </c>
       <c r="CY15" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-9.4267285986744748E-2</v>
       </c>
     </row>
     <row r="16" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -4730,13 +4793,15 @@
         <v>76</v>
       </c>
       <c r="CT16" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CU16" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CU16" s="15">
+        <v>14162</v>
+      </c>
       <c r="CV16" s="33"/>
       <c r="CW16" s="10">
         <f t="shared" si="29"/>
-        <v>-12269</v>
+        <v>1893</v>
       </c>
       <c r="CX16" s="12">
         <f t="shared" si="30"/>
@@ -4963,11 +5028,13 @@
       <c r="CL17" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="CM17" s="15"/>
+      <c r="CM17" s="15">
+        <v>31</v>
+      </c>
       <c r="CN17" s="33"/>
       <c r="CO17" s="10">
         <f t="shared" si="26"/>
-        <v>-9</v>
+        <v>22</v>
       </c>
       <c r="CP17" s="12">
         <f t="shared" si="27"/>
@@ -4979,13 +5046,15 @@
       </c>
       <c r="CS17" s="14"/>
       <c r="CT17" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="CU17" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="CU17" s="15">
+        <v>24</v>
+      </c>
       <c r="CV17" s="33"/>
       <c r="CW17" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="CX17" s="12">
         <f t="shared" si="30"/>
@@ -5255,18 +5324,23 @@
       <c r="CT18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV18" s="12"/>
+      <c r="CU18" s="10">
+        <v>229</v>
+      </c>
+      <c r="CV18" s="12">
+        <v>251878</v>
+      </c>
       <c r="CW18" s="10">
         <f t="shared" si="29"/>
-        <v>-210</v>
+        <v>19</v>
       </c>
       <c r="CX18" s="12">
         <f t="shared" si="30"/>
-        <v>-238942</v>
+        <v>12936</v>
       </c>
       <c r="CY18" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>5.4138661265076882E-2</v>
       </c>
     </row>
     <row r="19" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -5528,18 +5602,23 @@
       <c r="CT19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV19" s="12"/>
+      <c r="CU19" s="10">
+        <v>288</v>
+      </c>
+      <c r="CV19" s="12">
+        <v>320232</v>
+      </c>
       <c r="CW19" s="10">
         <f t="shared" si="29"/>
-        <v>-269</v>
+        <v>19</v>
       </c>
       <c r="CX19" s="12">
         <f t="shared" si="30"/>
-        <v>-316922</v>
+        <v>3310</v>
       </c>
       <c r="CY19" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>1.0444210247316375E-2</v>
       </c>
     </row>
     <row r="20" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -5801,18 +5880,23 @@
       <c r="CT20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV20" s="12"/>
+      <c r="CU20" s="10">
+        <v>94</v>
+      </c>
+      <c r="CV20" s="12">
+        <v>473788</v>
+      </c>
       <c r="CW20" s="10">
         <f t="shared" si="29"/>
-        <v>-83</v>
+        <v>11</v>
       </c>
       <c r="CX20" s="12">
         <f t="shared" si="30"/>
-        <v>-435686</v>
+        <v>38102</v>
       </c>
       <c r="CY20" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>8.7452890384359383E-2</v>
       </c>
     </row>
     <row r="21" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6074,18 +6158,23 @@
       <c r="CT21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CV21" s="12"/>
+      <c r="CU21" s="10">
+        <v>97</v>
+      </c>
+      <c r="CV21" s="12">
+        <v>1512190</v>
+      </c>
       <c r="CW21" s="10">
         <f t="shared" si="29"/>
-        <v>-33</v>
+        <v>64</v>
       </c>
       <c r="CX21" s="12">
         <f t="shared" si="30"/>
-        <v>-553524</v>
+        <v>958666</v>
       </c>
       <c r="CY21" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>1.7319321294108294</v>
       </c>
     </row>
     <row r="22" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6347,18 +6436,23 @@
       <c r="CT22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV22" s="12"/>
+      <c r="CU22" s="10">
+        <v>12</v>
+      </c>
+      <c r="CV22" s="12">
+        <v>75680</v>
+      </c>
       <c r="CW22" s="10">
         <f t="shared" si="29"/>
-        <v>-19</v>
+        <v>-7</v>
       </c>
       <c r="CX22" s="12">
         <f t="shared" si="30"/>
-        <v>-118310</v>
+        <v>-42630</v>
       </c>
       <c r="CY22" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.36032457104217736</v>
       </c>
     </row>
     <row r="23" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6620,18 +6714,23 @@
       <c r="CT23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV23" s="12"/>
+      <c r="CU23" s="10">
+        <v>18</v>
+      </c>
+      <c r="CV23" s="12">
+        <v>634948</v>
+      </c>
       <c r="CW23" s="10">
         <f t="shared" si="29"/>
-        <v>-25</v>
+        <v>-7</v>
       </c>
       <c r="CX23" s="12">
         <f t="shared" si="30"/>
-        <v>-952124</v>
+        <v>-317176</v>
       </c>
       <c r="CY23" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.3331246770378648</v>
       </c>
     </row>
     <row r="24" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -6893,18 +6992,23 @@
       <c r="CT24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV24" s="12"/>
+      <c r="CU24" s="10">
+        <v>52</v>
+      </c>
+      <c r="CV24" s="12">
+        <v>1137143</v>
+      </c>
       <c r="CW24" s="10">
         <f t="shared" si="29"/>
-        <v>-38</v>
+        <v>14</v>
       </c>
       <c r="CX24" s="12">
         <f t="shared" si="30"/>
-        <v>-884381</v>
+        <v>252762</v>
       </c>
       <c r="CY24" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.28580668286632122</v>
       </c>
     </row>
     <row r="25" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -7166,18 +7270,23 @@
       <c r="CT25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV25" s="12"/>
+      <c r="CU25" s="10">
+        <v>68</v>
+      </c>
+      <c r="CV25" s="12">
+        <v>3324000</v>
+      </c>
       <c r="CW25" s="10">
         <f t="shared" si="29"/>
-        <v>-259</v>
+        <v>-191</v>
       </c>
       <c r="CX25" s="12">
         <f t="shared" si="30"/>
-        <v>-11919143</v>
+        <v>-8595143</v>
       </c>
       <c r="CY25" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.72112088931226015</v>
       </c>
     </row>
     <row r="26" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -7440,19 +7549,23 @@
         <v>12</v>
       </c>
       <c r="CT26" s="9"/>
-      <c r="CU26" s="8"/>
-      <c r="CV26" s="7"/>
+      <c r="CU26" s="8">
+        <v>858</v>
+      </c>
+      <c r="CV26" s="7">
+        <v>7729859</v>
+      </c>
       <c r="CW26" s="27">
         <f t="shared" si="29"/>
-        <v>-936</v>
+        <v>-78</v>
       </c>
       <c r="CX26" s="28">
         <f t="shared" si="30"/>
-        <v>-15419032</v>
+        <v>-7689173</v>
       </c>
       <c r="CY26" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.49868065647700843</v>
       </c>
     </row>
     <row r="27" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -7715,13 +7828,15 @@
         <v>77</v>
       </c>
       <c r="CT27" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CU27" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CU27" s="15">
+        <v>11811</v>
+      </c>
       <c r="CV27" s="33"/>
       <c r="CW27" s="10">
         <f t="shared" si="29"/>
-        <v>-7954</v>
+        <v>3857</v>
       </c>
       <c r="CX27" s="12">
         <f t="shared" si="30"/>
@@ -7948,11 +8063,13 @@
       <c r="CL28" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="CM28" s="15"/>
+      <c r="CM28" s="15">
+        <v>16</v>
+      </c>
       <c r="CN28" s="33"/>
       <c r="CO28" s="10">
         <f t="shared" si="26"/>
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CP28" s="12">
         <f t="shared" si="27"/>
@@ -7964,13 +8081,15 @@
       </c>
       <c r="CS28" s="14"/>
       <c r="CT28" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="CU28" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="CU28" s="15">
+        <v>12</v>
+      </c>
       <c r="CV28" s="33"/>
       <c r="CW28" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="CX28" s="12">
         <f t="shared" si="30"/>
@@ -8240,18 +8359,23 @@
       <c r="CT29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV29" s="12"/>
+      <c r="CU29" s="10">
+        <v>145</v>
+      </c>
+      <c r="CV29" s="12">
+        <v>127560</v>
+      </c>
       <c r="CW29" s="10">
         <f t="shared" si="29"/>
-        <v>-132</v>
+        <v>13</v>
       </c>
       <c r="CX29" s="12">
         <f t="shared" si="30"/>
-        <v>-122216</v>
+        <v>5344</v>
       </c>
       <c r="CY29" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>4.3725862407540748E-2</v>
       </c>
     </row>
     <row r="30" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -8513,18 +8637,23 @@
       <c r="CT30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV30" s="12"/>
+      <c r="CU30" s="10">
+        <v>125</v>
+      </c>
+      <c r="CV30" s="12">
+        <v>104487</v>
+      </c>
       <c r="CW30" s="10">
         <f t="shared" si="29"/>
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="CX30" s="12">
         <f t="shared" si="30"/>
-        <v>-72145</v>
+        <v>32342</v>
       </c>
       <c r="CY30" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.44829163490193363</v>
       </c>
     </row>
     <row r="31" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -8786,18 +8915,23 @@
       <c r="CT31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV31" s="12"/>
+      <c r="CU31" s="10">
+        <v>38</v>
+      </c>
+      <c r="CV31" s="12">
+        <v>196663</v>
+      </c>
       <c r="CW31" s="10">
         <f t="shared" si="29"/>
-        <v>-13</v>
+        <v>25</v>
       </c>
       <c r="CX31" s="12">
         <f t="shared" si="30"/>
-        <v>-87210</v>
+        <v>109453</v>
       </c>
       <c r="CY31" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>1.2550510262584567</v>
       </c>
     </row>
     <row r="32" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9059,18 +9193,23 @@
       <c r="CT32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CV32" s="12"/>
+      <c r="CU32" s="10">
+        <v>23</v>
+      </c>
+      <c r="CV32" s="12">
+        <v>335048</v>
+      </c>
       <c r="CW32" s="10">
         <f t="shared" si="29"/>
-        <v>-21</v>
+        <v>2</v>
       </c>
       <c r="CX32" s="12">
         <f t="shared" si="30"/>
-        <v>-345619</v>
+        <v>-10571</v>
       </c>
       <c r="CY32" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-3.0585702753610191E-2</v>
       </c>
     </row>
     <row r="33" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9332,18 +9471,23 @@
       <c r="CT33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV33" s="12"/>
+      <c r="CU33" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV33" s="12">
+        <v>33020</v>
+      </c>
       <c r="CW33" s="10">
         <f t="shared" si="29"/>
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="CX33" s="12">
         <f t="shared" si="30"/>
-        <v>-34040</v>
+        <v>-1020</v>
       </c>
       <c r="CY33" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-2.9964747356051705E-2</v>
       </c>
     </row>
     <row r="34" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9605,18 +9749,23 @@
       <c r="CT34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV34" s="12"/>
+      <c r="CU34" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV34" s="12">
+        <v>202709</v>
+      </c>
       <c r="CW34" s="10">
         <f t="shared" si="29"/>
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="CX34" s="12">
         <f t="shared" si="30"/>
-        <v>-114952</v>
+        <v>87757</v>
       </c>
       <c r="CY34" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.76342299394529889</v>
       </c>
     </row>
     <row r="35" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -9878,18 +10027,23 @@
       <c r="CT35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV35" s="12"/>
+      <c r="CU35" s="10">
+        <v>15</v>
+      </c>
+      <c r="CV35" s="12">
+        <v>325333</v>
+      </c>
       <c r="CW35" s="10">
         <f t="shared" si="29"/>
-        <v>-14</v>
+        <v>1</v>
       </c>
       <c r="CX35" s="12">
         <f t="shared" si="30"/>
-        <v>-291238</v>
+        <v>34095</v>
       </c>
       <c r="CY35" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.11706920113446734</v>
       </c>
     </row>
     <row r="36" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -10151,18 +10305,23 @@
       <c r="CT36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV36" s="12"/>
+      <c r="CU36" s="10">
+        <v>54</v>
+      </c>
+      <c r="CV36" s="12">
+        <v>2582005</v>
+      </c>
       <c r="CW36" s="10">
         <f t="shared" si="29"/>
-        <v>-108</v>
+        <v>-54</v>
       </c>
       <c r="CX36" s="12">
         <f t="shared" si="30"/>
-        <v>-5045905</v>
+        <v>-2463900</v>
       </c>
       <c r="CY36" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.48829694574115051</v>
       </c>
     </row>
     <row r="37" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -10425,19 +10584,23 @@
         <v>11</v>
       </c>
       <c r="CT37" s="9"/>
-      <c r="CU37" s="8"/>
-      <c r="CV37" s="7"/>
+      <c r="CU37" s="8">
+        <v>416</v>
+      </c>
+      <c r="CV37" s="7">
+        <v>3906825</v>
+      </c>
       <c r="CW37" s="27">
         <f t="shared" si="29"/>
-        <v>-372</v>
+        <v>44</v>
       </c>
       <c r="CX37" s="28">
         <f t="shared" si="30"/>
-        <v>-6113325</v>
+        <v>-2206500</v>
       </c>
       <c r="CY37" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.36093288022475495</v>
       </c>
     </row>
     <row r="38" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -10700,13 +10863,15 @@
         <v>81</v>
       </c>
       <c r="CT38" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="CU38" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="CU38" s="15">
+        <v>6363</v>
+      </c>
       <c r="CV38" s="33"/>
       <c r="CW38" s="10">
         <f t="shared" si="29"/>
-        <v>-5160</v>
+        <v>1203</v>
       </c>
       <c r="CX38" s="12">
         <f t="shared" si="30"/>
@@ -10933,11 +11098,13 @@
       <c r="CL39" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="CM39" s="15"/>
+      <c r="CM39" s="15">
+        <v>13</v>
+      </c>
       <c r="CN39" s="33"/>
       <c r="CO39" s="10">
         <f t="shared" si="26"/>
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CP39" s="12">
         <f t="shared" si="27"/>
@@ -10949,13 +11116,15 @@
       </c>
       <c r="CS39" s="14"/>
       <c r="CT39" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="CU39" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="CU39" s="15">
+        <v>11</v>
+      </c>
       <c r="CV39" s="33"/>
       <c r="CW39" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="CX39" s="12">
         <f t="shared" si="30"/>
@@ -11225,18 +11394,23 @@
       <c r="CT40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV40" s="12"/>
+      <c r="CU40" s="10">
+        <v>186</v>
+      </c>
+      <c r="CV40" s="12">
+        <v>183242</v>
+      </c>
       <c r="CW40" s="10">
         <f t="shared" si="29"/>
-        <v>-216</v>
+        <v>-30</v>
       </c>
       <c r="CX40" s="12">
         <f t="shared" si="30"/>
-        <v>-223403</v>
+        <v>-40161</v>
       </c>
       <c r="CY40" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.17976929584651952</v>
       </c>
     </row>
     <row r="41" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -11498,18 +11672,23 @@
       <c r="CT41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV41" s="12"/>
+      <c r="CU41" s="10">
+        <v>105</v>
+      </c>
+      <c r="CV41" s="12">
+        <v>119086</v>
+      </c>
       <c r="CW41" s="10">
         <f t="shared" si="29"/>
-        <v>-108</v>
+        <v>-3</v>
       </c>
       <c r="CX41" s="12">
         <f t="shared" si="30"/>
-        <v>-107782</v>
+        <v>11304</v>
       </c>
       <c r="CY41" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.10487836558980164</v>
       </c>
     </row>
     <row r="42" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -11771,18 +11950,23 @@
       <c r="CT42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV42" s="12"/>
+      <c r="CU42" s="10">
+        <v>32</v>
+      </c>
+      <c r="CV42" s="12">
+        <v>176687</v>
+      </c>
       <c r="CW42" s="10">
         <f t="shared" si="29"/>
-        <v>-11</v>
+        <v>21</v>
       </c>
       <c r="CX42" s="12">
         <f t="shared" si="30"/>
-        <v>-70086</v>
+        <v>106601</v>
       </c>
       <c r="CY42" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>1.5210027680278515</v>
       </c>
     </row>
     <row r="43" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12044,18 +12228,23 @@
       <c r="CT43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CV43" s="12"/>
+      <c r="CU43" s="10">
+        <v>29</v>
+      </c>
+      <c r="CV43" s="12">
+        <v>395333</v>
+      </c>
       <c r="CW43" s="10">
         <f t="shared" si="29"/>
-        <v>-15</v>
+        <v>14</v>
       </c>
       <c r="CX43" s="12">
         <f t="shared" si="30"/>
-        <v>-273333</v>
+        <v>122000</v>
       </c>
       <c r="CY43" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.44634200773415578</v>
       </c>
     </row>
     <row r="44" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12317,7 +12506,12 @@
       <c r="CT44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV44" s="12"/>
+      <c r="CU44" s="10">
+        <v>0</v>
+      </c>
+      <c r="CV44" s="12">
+        <v>0</v>
+      </c>
       <c r="CW44" s="10">
         <f t="shared" si="29"/>
         <v>-6</v>
@@ -12590,18 +12784,23 @@
       <c r="CT45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV45" s="12"/>
+      <c r="CU45" s="10">
+        <v>12</v>
+      </c>
+      <c r="CV45" s="12">
+        <v>361305</v>
+      </c>
       <c r="CW45" s="10">
         <f t="shared" si="29"/>
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="CX45" s="12">
         <f t="shared" si="30"/>
-        <v>-312388</v>
+        <v>48917</v>
       </c>
       <c r="CY45" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.15659052204310026</v>
       </c>
     </row>
     <row r="46" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -12863,18 +13062,23 @@
       <c r="CT46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV46" s="12"/>
+      <c r="CU46" s="10">
+        <v>18</v>
+      </c>
+      <c r="CV46" s="12">
+        <v>348857</v>
+      </c>
       <c r="CW46" s="10">
         <f t="shared" si="29"/>
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="CX46" s="12">
         <f t="shared" si="30"/>
-        <v>-310381</v>
+        <v>38476</v>
       </c>
       <c r="CY46" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.12396377355572667</v>
       </c>
     </row>
     <row r="47" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -13136,18 +13340,23 @@
       <c r="CT47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV47" s="12"/>
+      <c r="CU47" s="10">
+        <v>47</v>
+      </c>
+      <c r="CV47" s="12">
+        <v>2164095</v>
+      </c>
       <c r="CW47" s="10">
         <f t="shared" si="29"/>
-        <v>-131</v>
+        <v>-84</v>
       </c>
       <c r="CX47" s="12">
         <f t="shared" si="30"/>
-        <v>-6077048</v>
+        <v>-3912953</v>
       </c>
       <c r="CY47" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.6438904217968987</v>
       </c>
     </row>
     <row r="48" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -13410,19 +13619,23 @@
         <v>10</v>
       </c>
       <c r="CT48" s="9"/>
-      <c r="CU48" s="8"/>
-      <c r="CV48" s="7"/>
+      <c r="CU48" s="8">
+        <v>429</v>
+      </c>
+      <c r="CV48" s="7">
+        <v>3748605</v>
+      </c>
       <c r="CW48" s="27">
         <f t="shared" si="29"/>
-        <v>-511</v>
+        <v>-82</v>
       </c>
       <c r="CX48" s="28">
         <f t="shared" si="30"/>
-        <v>-7413361</v>
+        <v>-3664756</v>
       </c>
       <c r="CY48" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.4943447378321385</v>
       </c>
     </row>
     <row r="49" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -13653,7 +13866,7 @@
         <v>84</v>
       </c>
       <c r="CT49" s="32" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="CU49" s="15"/>
       <c r="CV49" s="33"/>
@@ -13886,11 +14099,13 @@
       <c r="CL50" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="CM50" s="15"/>
+      <c r="CM50" s="15">
+        <v>1</v>
+      </c>
       <c r="CN50" s="33"/>
       <c r="CO50" s="10">
         <f t="shared" si="26"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CP50" s="12">
         <f t="shared" si="27"/>
@@ -13902,13 +14117,15 @@
       </c>
       <c r="CS50" s="14"/>
       <c r="CT50" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="CU50" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="CU50" s="15">
+        <v>6</v>
+      </c>
       <c r="CV50" s="33"/>
       <c r="CW50" s="10">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CX50" s="12">
         <f t="shared" si="30"/>
@@ -14178,18 +14395,23 @@
       <c r="CT51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="CV51" s="12"/>
+      <c r="CU51" s="10">
+        <v>228</v>
+      </c>
+      <c r="CV51" s="12">
+        <v>233807</v>
+      </c>
       <c r="CW51" s="10">
         <f t="shared" si="29"/>
-        <v>-177</v>
+        <v>51</v>
       </c>
       <c r="CX51" s="12">
         <f t="shared" si="30"/>
-        <v>-167083</v>
+        <v>66724</v>
       </c>
       <c r="CY51" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.3993464326113369</v>
       </c>
     </row>
     <row r="52" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -14451,18 +14673,23 @@
       <c r="CT52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="CV52" s="12"/>
+      <c r="CU52" s="10">
+        <v>105</v>
+      </c>
+      <c r="CV52" s="12">
+        <v>102630</v>
+      </c>
       <c r="CW52" s="10">
         <f t="shared" si="29"/>
-        <v>-69</v>
+        <v>36</v>
       </c>
       <c r="CX52" s="12">
         <f t="shared" si="30"/>
-        <v>-69724</v>
+        <v>32906</v>
       </c>
       <c r="CY52" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.47194653204061732</v>
       </c>
     </row>
     <row r="53" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -14724,18 +14951,23 @@
       <c r="CT53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="CV53" s="12"/>
+      <c r="CU53" s="10">
+        <v>32</v>
+      </c>
+      <c r="CV53" s="12">
+        <v>158457</v>
+      </c>
       <c r="CW53" s="10">
         <f t="shared" si="29"/>
-        <v>-16</v>
+        <v>16</v>
       </c>
       <c r="CX53" s="12">
         <f t="shared" si="30"/>
-        <v>-96800</v>
+        <v>61657</v>
       </c>
       <c r="CY53" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.63695247933884303</v>
       </c>
     </row>
     <row r="54" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -14997,18 +15229,23 @@
       <c r="CT54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="CV54" s="12"/>
+      <c r="CU54" s="10">
+        <v>24</v>
+      </c>
+      <c r="CV54" s="12">
+        <v>344857</v>
+      </c>
       <c r="CW54" s="10">
         <f t="shared" si="29"/>
-        <v>-16</v>
+        <v>8</v>
       </c>
       <c r="CX54" s="12">
         <f t="shared" si="30"/>
-        <v>-252762</v>
+        <v>92095</v>
       </c>
       <c r="CY54" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.36435461026578364</v>
       </c>
     </row>
     <row r="55" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15270,18 +15507,23 @@
       <c r="CT55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="CV55" s="12"/>
+      <c r="CU55" s="10">
+        <v>6</v>
+      </c>
+      <c r="CV55" s="12">
+        <v>24540</v>
+      </c>
       <c r="CW55" s="10">
         <f t="shared" si="29"/>
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="CX55" s="12">
         <f t="shared" si="30"/>
-        <v>-42320</v>
+        <v>-17780</v>
       </c>
       <c r="CY55" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.42013232514177695</v>
       </c>
     </row>
     <row r="56" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15543,18 +15785,23 @@
       <c r="CT56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="CV56" s="12"/>
+      <c r="CU56" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV56" s="12">
+        <v>306576</v>
+      </c>
       <c r="CW56" s="10">
         <f t="shared" si="29"/>
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CX56" s="12">
         <f t="shared" si="30"/>
-        <v>-24667</v>
+        <v>281909</v>
       </c>
       <c r="CY56" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>11.428588802854016</v>
       </c>
     </row>
     <row r="57" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -15816,18 +16063,23 @@
       <c r="CT57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="CV57" s="12"/>
+      <c r="CU57" s="10">
+        <v>20</v>
+      </c>
+      <c r="CV57" s="12">
+        <v>491429</v>
+      </c>
       <c r="CW57" s="10">
         <f t="shared" si="29"/>
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="CX57" s="12">
         <f t="shared" si="30"/>
-        <v>-285048</v>
+        <v>206381</v>
       </c>
       <c r="CY57" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>0.72402191911537706</v>
       </c>
     </row>
     <row r="58" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
@@ -16089,18 +16341,23 @@
       <c r="CT58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="CV58" s="12"/>
+      <c r="CU58" s="10">
+        <v>80</v>
+      </c>
+      <c r="CV58" s="12">
+        <v>3812050</v>
+      </c>
       <c r="CW58" s="10">
         <f t="shared" si="29"/>
-        <v>-129</v>
+        <v>-49</v>
       </c>
       <c r="CX58" s="12">
         <f t="shared" si="30"/>
-        <v>-5971261</v>
+        <v>-2159211</v>
       </c>
       <c r="CY58" s="11">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.36160050615774458</v>
       </c>
     </row>
     <row r="59" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -16363,19 +16620,23 @@
         <v>1</v>
       </c>
       <c r="CT59" s="9"/>
-      <c r="CU59" s="8"/>
-      <c r="CV59" s="7"/>
+      <c r="CU59" s="8">
+        <v>503</v>
+      </c>
+      <c r="CV59" s="7">
+        <v>5474346</v>
+      </c>
       <c r="CW59" s="27">
         <f t="shared" si="29"/>
-        <v>-428</v>
+        <v>75</v>
       </c>
       <c r="CX59" s="28">
         <f t="shared" si="30"/>
-        <v>-6909665</v>
+        <v>-1435319</v>
       </c>
       <c r="CY59" s="29">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.20772627905983865</v>
       </c>
     </row>
     <row r="60" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
@@ -16638,19 +16899,23 @@
         <v>0</v>
       </c>
       <c r="CT60" s="4"/>
-      <c r="CU60" s="3"/>
-      <c r="CV60" s="2"/>
+      <c r="CU60" s="3">
+        <v>3847</v>
+      </c>
+      <c r="CV60" s="2">
+        <v>43997165</v>
+      </c>
       <c r="CW60" s="6">
         <f t="shared" si="29"/>
-        <v>-3547</v>
+        <v>300</v>
       </c>
       <c r="CX60" s="5">
         <f t="shared" si="30"/>
-        <v>-61401032</v>
+        <v>-17403867</v>
       </c>
       <c r="CY60" s="30">
         <f t="shared" si="31"/>
-        <v>-1</v>
+        <v>-0.28344583849991317</v>
       </c>
     </row>
   </sheetData>
